--- a/Unity/Assets/Config/Excel/ItemConfig.xlsx
+++ b/Unity/Assets/Config/Excel/ItemConfig.xlsx
@@ -10,7 +10,7 @@
     <sheet name="ItemProto" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ItemProto!$R$1:$R$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ItemProto!$R$1:$R$16</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -442,7 +442,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="74">
   <si>
     <t xml:space="preserve"> </t>
   </si>
@@ -611,7 +611,7 @@
     <t>string</t>
   </si>
   <si>
-    <t>（测试）元宝</t>
+    <t>（测试）声望</t>
   </si>
   <si>
     <t>1</t>
@@ -621,6 +621,9 @@
   </si>
   <si>
     <t>嘿嘿嘿!</t>
+  </si>
+  <si>
+    <t>（测试）元宝</t>
   </si>
   <si>
     <t>（测试）经验</t>
@@ -690,7 +693,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="34">
+  <fonts count="35">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -915,7 +918,12 @@
     <font>
       <b/>
       <sz val="9"/>
-      <name val="Tahoma"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -926,7 +934,7 @@
     <font>
       <b/>
       <sz val="9"/>
-      <name val="宋体"/>
+      <name val="Tahoma"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -7650,7 +7658,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2">
-    <tableStyle name="MySqlDefault" count="2" xr9:uid="{29C623DD-F4B2-4465-9227-8CA2C6ACDD18}">
+    <tableStyle name="MySqlDefault" count="2" xr9:uid="{67121B24-83FB-4E7D-BD55-E68D33E68AAA}">
       <tableStyleElement type="wholeTable" dxfId="1"/>
       <tableStyleElement type="headerRow" dxfId="0"/>
     </tableStyle>
@@ -7950,7 +7958,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:Z15"/>
+  <dimension ref="C1:Z16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="2" width="10.875" customWidth="1"/>
@@ -8201,7 +8209,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="6" ht="20.1" customHeight="1" spans="3:26">
+    <row r="6" customFormat="1" ht="20.1" customHeight="1" spans="3:26">
       <c r="C6" s="7">
         <v>1</v>
       </c>
@@ -8280,8 +8288,8 @@
       <c r="D7" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="E7" s="8">
-        <v>2</v>
+      <c r="E7" s="8" t="s">
+        <v>51</v>
       </c>
       <c r="F7" s="9">
         <v>0</v>
@@ -8327,10 +8335,10 @@
       </c>
       <c r="T7" s="11"/>
       <c r="U7" s="12" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="V7" s="13" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="W7" s="8">
         <v>0</v>
@@ -8350,16 +8358,16 @@
         <v>3</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>58</v>
+        <v>55</v>
+      </c>
+      <c r="E8" s="8">
+        <v>2</v>
       </c>
       <c r="F8" s="9">
         <v>0</v>
       </c>
-      <c r="G8" s="10" t="s">
-        <v>59</v>
+      <c r="G8" s="10">
+        <v>3</v>
       </c>
       <c r="H8" s="8">
         <v>0</v>
@@ -8399,9 +8407,11 @@
       </c>
       <c r="T8" s="11"/>
       <c r="U8" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="V8" s="13"/>
+        <v>56</v>
+      </c>
+      <c r="V8" s="13" t="s">
+        <v>57</v>
+      </c>
       <c r="W8" s="8">
         <v>0</v>
       </c>
@@ -8420,16 +8430,16 @@
         <v>4</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="E9" s="8">
-        <v>4</v>
+        <v>58</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>59</v>
       </c>
       <c r="F9" s="9">
         <v>0</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H9" s="8">
         <v>0</v>
@@ -8469,7 +8479,7 @@
       </c>
       <c r="T9" s="11"/>
       <c r="U9" s="12" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="V9" s="13"/>
       <c r="W9" s="8">
@@ -8490,16 +8500,16 @@
         <v>5</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E10" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F10" s="9">
         <v>0</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H10" s="8">
         <v>0</v>
@@ -8539,7 +8549,7 @@
       </c>
       <c r="T10" s="11"/>
       <c r="U10" s="12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="V10" s="13"/>
       <c r="W10" s="8">
@@ -8555,69 +8565,73 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:26">
+    <row r="11" ht="20.1" customHeight="1" spans="3:26">
       <c r="C11" s="7">
         <v>6</v>
       </c>
-      <c r="D11" s="14" t="s">
+      <c r="D11" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="E11" s="8">
+        <v>5</v>
+      </c>
+      <c r="F11" s="9">
+        <v>0</v>
+      </c>
+      <c r="G11" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="H11" s="8">
+        <v>0</v>
+      </c>
+      <c r="I11" s="8">
+        <v>0</v>
+      </c>
+      <c r="J11" s="8">
+        <v>1</v>
+      </c>
+      <c r="K11" s="8">
+        <v>0</v>
+      </c>
+      <c r="L11" s="11">
+        <v>0</v>
+      </c>
+      <c r="M11" s="8">
+        <v>999999</v>
+      </c>
+      <c r="N11" s="11">
+        <v>1</v>
+      </c>
+      <c r="O11" s="8">
+        <v>0</v>
+      </c>
+      <c r="P11" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="8">
+        <v>0</v>
+      </c>
+      <c r="R11" s="8">
+        <v>0</v>
+      </c>
+      <c r="S11" s="8">
+        <v>0</v>
+      </c>
+      <c r="T11" s="11"/>
+      <c r="U11" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="E11" s="14">
-        <v>10000101</v>
-      </c>
-      <c r="F11" s="15">
-        <v>15410003</v>
-      </c>
-      <c r="G11" s="16">
-        <v>3</v>
-      </c>
-      <c r="H11" s="17">
-        <v>40</v>
-      </c>
-      <c r="I11" s="17">
-        <v>0</v>
-      </c>
-      <c r="J11" s="17">
-        <v>3</v>
-      </c>
-      <c r="K11" s="17">
+      <c r="V11" s="13"/>
+      <c r="W11" s="8">
+        <v>0</v>
+      </c>
+      <c r="X11" s="8">
         <v>1</v>
       </c>
-      <c r="L11" s="18">
-        <v>2</v>
-      </c>
-      <c r="M11" s="17">
-        <v>1</v>
-      </c>
-      <c r="N11" s="18">
-        <v>1</v>
-      </c>
-      <c r="O11" s="17">
-        <v>15375</v>
-      </c>
-      <c r="P11" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="17"/>
-      <c r="R11" s="17"/>
-      <c r="S11" s="17">
-        <v>0</v>
-      </c>
-      <c r="T11" s="18" t="s">
-        <v>66</v>
-      </c>
-      <c r="U11" s="19"/>
-      <c r="V11" s="20"/>
-      <c r="W11" s="17">
-        <v>0</v>
-      </c>
-      <c r="X11" s="17">
-        <v>0</v>
-      </c>
-      <c r="Y11" s="17">
-        <v>0</v>
-      </c>
-      <c r="Z11" s="17">
+      <c r="Y11" s="8">
+        <v>0</v>
+      </c>
+      <c r="Z11" s="8">
         <v>0</v>
       </c>
     </row>
@@ -8626,16 +8640,16 @@
         <v>7</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E12" s="14">
         <v>10000101</v>
       </c>
       <c r="F12" s="15">
-        <v>15410004</v>
+        <v>15410003</v>
       </c>
       <c r="G12" s="16">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H12" s="17">
         <v>40</v>
@@ -8659,7 +8673,7 @@
         <v>1</v>
       </c>
       <c r="O12" s="17">
-        <v>18450</v>
+        <v>15375</v>
       </c>
       <c r="P12" s="8">
         <v>0</v>
@@ -8670,7 +8684,7 @@
         <v>0</v>
       </c>
       <c r="T12" s="18" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="U12" s="19"/>
       <c r="V12" s="20"/>
@@ -8692,40 +8706,40 @@
         <v>8</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E13" s="14">
         <v>10000101</v>
       </c>
       <c r="F13" s="15">
-        <v>0</v>
+        <v>15410004</v>
       </c>
       <c r="G13" s="16">
+        <v>4</v>
+      </c>
+      <c r="H13" s="17">
+        <v>40</v>
+      </c>
+      <c r="I13" s="17">
+        <v>0</v>
+      </c>
+      <c r="J13" s="17">
         <v>3</v>
       </c>
-      <c r="H13" s="17">
+      <c r="K13" s="17">
         <v>1</v>
       </c>
-      <c r="I13" s="17">
-        <v>0</v>
-      </c>
-      <c r="J13" s="17">
+      <c r="L13" s="18">
+        <v>2</v>
+      </c>
+      <c r="M13" s="17">
         <v>1</v>
-      </c>
-      <c r="K13" s="17">
-        <v>0</v>
-      </c>
-      <c r="L13" s="18">
-        <v>0</v>
-      </c>
-      <c r="M13" s="17">
-        <v>99</v>
       </c>
       <c r="N13" s="18">
         <v>1</v>
       </c>
       <c r="O13" s="17">
-        <v>19125</v>
+        <v>18450</v>
       </c>
       <c r="P13" s="8">
         <v>0</v>
@@ -8736,7 +8750,7 @@
         <v>0</v>
       </c>
       <c r="T13" s="18" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="U13" s="19"/>
       <c r="V13" s="20"/>
@@ -8758,7 +8772,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E14" s="14">
         <v>10000101</v>
@@ -8802,7 +8816,7 @@
         <v>0</v>
       </c>
       <c r="T14" s="18" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="U14" s="19"/>
       <c r="V14" s="20"/>
@@ -8862,15 +8876,13 @@
       <c r="P15" s="8">
         <v>0</v>
       </c>
-      <c r="Q15" s="17">
-        <v>2000</v>
-      </c>
+      <c r="Q15" s="17"/>
       <c r="R15" s="17"/>
       <c r="S15" s="17">
         <v>0</v>
       </c>
       <c r="T15" s="18" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="U15" s="19"/>
       <c r="V15" s="20"/>
@@ -8887,8 +8899,76 @@
         <v>0</v>
       </c>
     </row>
+    <row r="16" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:26">
+      <c r="C16" s="7">
+        <v>11</v>
+      </c>
+      <c r="D16" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="E16" s="14">
+        <v>10000101</v>
+      </c>
+      <c r="F16" s="15">
+        <v>0</v>
+      </c>
+      <c r="G16" s="16">
+        <v>3</v>
+      </c>
+      <c r="H16" s="17">
+        <v>1</v>
+      </c>
+      <c r="I16" s="17">
+        <v>0</v>
+      </c>
+      <c r="J16" s="17">
+        <v>1</v>
+      </c>
+      <c r="K16" s="17">
+        <v>0</v>
+      </c>
+      <c r="L16" s="18">
+        <v>0</v>
+      </c>
+      <c r="M16" s="17">
+        <v>99</v>
+      </c>
+      <c r="N16" s="18">
+        <v>1</v>
+      </c>
+      <c r="O16" s="17">
+        <v>19125</v>
+      </c>
+      <c r="P16" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="17">
+        <v>2000</v>
+      </c>
+      <c r="R16" s="17"/>
+      <c r="S16" s="17">
+        <v>0</v>
+      </c>
+      <c r="T16" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="U16" s="19"/>
+      <c r="V16" s="20"/>
+      <c r="W16" s="17">
+        <v>0</v>
+      </c>
+      <c r="X16" s="17">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="17">
+        <v>0</v>
+      </c>
+      <c r="Z16" s="17">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="R1:R15" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="R1:R16" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Unity/Assets/Config/Excel/ItemConfig.xlsx
+++ b/Unity/Assets/Config/Excel/ItemConfig.xlsx
@@ -442,7 +442,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="88">
   <si>
     <t xml:space="preserve"> </t>
   </si>
@@ -681,6 +681,48 @@
   </si>
   <si>
     <t>（测试）抓捕器</t>
+  </si>
+  <si>
+    <t>荣誉级勋章1级</t>
+  </si>
+  <si>
+    <t>荣誉级勋章2级</t>
+  </si>
+  <si>
+    <t>荣誉级勋章3级</t>
+  </si>
+  <si>
+    <t>荣誉级勋章4级</t>
+  </si>
+  <si>
+    <t>圣战级勋章1级</t>
+  </si>
+  <si>
+    <t>圣战级勋章2级</t>
+  </si>
+  <si>
+    <t>白虎印</t>
+  </si>
+  <si>
+    <t>朱雀印</t>
+  </si>
+  <si>
+    <t>青龙印</t>
+  </si>
+  <si>
+    <t>无双勋章</t>
+  </si>
+  <si>
+    <t>荒古勋章</t>
+  </si>
+  <si>
+    <t>星辰勋章</t>
+  </si>
+  <si>
+    <t>战神凭证</t>
+  </si>
+  <si>
+    <t>帝释天勋章</t>
   </si>
 </sst>
 </file>
@@ -7958,7 +8000,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:Z16"/>
+  <dimension ref="C1:Z43"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="2" width="10.875" customWidth="1"/>
@@ -8942,9 +8984,7 @@
       <c r="P16" s="8">
         <v>0</v>
       </c>
-      <c r="Q16" s="17">
-        <v>2000</v>
-      </c>
+      <c r="Q16" s="17"/>
       <c r="R16" s="17"/>
       <c r="S16" s="17">
         <v>0</v>
@@ -8966,6 +9006,1137 @@
       <c r="Z16" s="17">
         <v>0</v>
       </c>
+    </row>
+    <row r="17" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:26">
+      <c r="C17" s="14">
+        <v>12</v>
+      </c>
+      <c r="D17" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="E17" s="14">
+        <v>10000101</v>
+      </c>
+      <c r="F17" s="14">
+        <v>0</v>
+      </c>
+      <c r="G17" s="14">
+        <v>3</v>
+      </c>
+      <c r="H17" s="17">
+        <v>1</v>
+      </c>
+      <c r="I17" s="17">
+        <v>0</v>
+      </c>
+      <c r="J17" s="17">
+        <v>1</v>
+      </c>
+      <c r="K17" s="17">
+        <v>0</v>
+      </c>
+      <c r="L17" s="18">
+        <v>0</v>
+      </c>
+      <c r="M17" s="17">
+        <v>99</v>
+      </c>
+      <c r="N17" s="18">
+        <v>1</v>
+      </c>
+      <c r="O17" s="17">
+        <v>19125</v>
+      </c>
+      <c r="P17" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="17"/>
+      <c r="R17" s="17"/>
+      <c r="S17" s="17">
+        <v>0</v>
+      </c>
+      <c r="T17" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="U17" s="19"/>
+      <c r="V17" s="20"/>
+      <c r="W17" s="17">
+        <v>0</v>
+      </c>
+      <c r="X17" s="17">
+        <v>0</v>
+      </c>
+      <c r="Y17" s="17">
+        <v>0</v>
+      </c>
+      <c r="Z17" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:26">
+      <c r="C18" s="14">
+        <v>13</v>
+      </c>
+      <c r="D18" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="E18" s="14">
+        <v>10000101</v>
+      </c>
+      <c r="F18" s="14">
+        <v>0</v>
+      </c>
+      <c r="G18" s="14">
+        <v>3</v>
+      </c>
+      <c r="H18" s="17">
+        <v>1</v>
+      </c>
+      <c r="I18" s="17">
+        <v>0</v>
+      </c>
+      <c r="J18" s="17">
+        <v>1</v>
+      </c>
+      <c r="K18" s="17">
+        <v>0</v>
+      </c>
+      <c r="L18" s="18">
+        <v>0</v>
+      </c>
+      <c r="M18" s="17">
+        <v>99</v>
+      </c>
+      <c r="N18" s="18">
+        <v>1</v>
+      </c>
+      <c r="O18" s="17">
+        <v>19125</v>
+      </c>
+      <c r="P18" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="17"/>
+      <c r="R18" s="17"/>
+      <c r="S18" s="17">
+        <v>0</v>
+      </c>
+      <c r="T18" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="U18" s="19"/>
+      <c r="V18" s="20"/>
+      <c r="W18" s="17">
+        <v>0</v>
+      </c>
+      <c r="X18" s="17">
+        <v>0</v>
+      </c>
+      <c r="Y18" s="17">
+        <v>0</v>
+      </c>
+      <c r="Z18" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:26">
+      <c r="C19" s="14">
+        <v>14</v>
+      </c>
+      <c r="D19" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="E19" s="14">
+        <v>10000101</v>
+      </c>
+      <c r="F19" s="14">
+        <v>0</v>
+      </c>
+      <c r="G19" s="14">
+        <v>3</v>
+      </c>
+      <c r="H19" s="17">
+        <v>1</v>
+      </c>
+      <c r="I19" s="17">
+        <v>0</v>
+      </c>
+      <c r="J19" s="17">
+        <v>1</v>
+      </c>
+      <c r="K19" s="17">
+        <v>0</v>
+      </c>
+      <c r="L19" s="18">
+        <v>0</v>
+      </c>
+      <c r="M19" s="17">
+        <v>99</v>
+      </c>
+      <c r="N19" s="18">
+        <v>1</v>
+      </c>
+      <c r="O19" s="17">
+        <v>19125</v>
+      </c>
+      <c r="P19" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="17"/>
+      <c r="R19" s="17"/>
+      <c r="S19" s="17">
+        <v>0</v>
+      </c>
+      <c r="T19" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="U19" s="19"/>
+      <c r="V19" s="20"/>
+      <c r="W19" s="17">
+        <v>0</v>
+      </c>
+      <c r="X19" s="17">
+        <v>0</v>
+      </c>
+      <c r="Y19" s="17">
+        <v>0</v>
+      </c>
+      <c r="Z19" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:26">
+      <c r="C20" s="14">
+        <v>15</v>
+      </c>
+      <c r="D20" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="E20" s="14">
+        <v>10000101</v>
+      </c>
+      <c r="F20" s="14">
+        <v>0</v>
+      </c>
+      <c r="G20" s="14">
+        <v>3</v>
+      </c>
+      <c r="H20" s="17">
+        <v>1</v>
+      </c>
+      <c r="I20" s="17">
+        <v>0</v>
+      </c>
+      <c r="J20" s="17">
+        <v>1</v>
+      </c>
+      <c r="K20" s="17">
+        <v>0</v>
+      </c>
+      <c r="L20" s="18">
+        <v>0</v>
+      </c>
+      <c r="M20" s="17">
+        <v>99</v>
+      </c>
+      <c r="N20" s="18">
+        <v>1</v>
+      </c>
+      <c r="O20" s="17">
+        <v>19125</v>
+      </c>
+      <c r="P20" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="17"/>
+      <c r="R20" s="17"/>
+      <c r="S20" s="17">
+        <v>0</v>
+      </c>
+      <c r="T20" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="U20" s="19"/>
+      <c r="V20" s="20"/>
+      <c r="W20" s="17">
+        <v>0</v>
+      </c>
+      <c r="X20" s="17">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="17">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:26">
+      <c r="C21" s="14">
+        <v>16</v>
+      </c>
+      <c r="D21" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="E21" s="14">
+        <v>10000101</v>
+      </c>
+      <c r="F21" s="14">
+        <v>0</v>
+      </c>
+      <c r="G21" s="14">
+        <v>3</v>
+      </c>
+      <c r="H21" s="17">
+        <v>1</v>
+      </c>
+      <c r="I21" s="17">
+        <v>0</v>
+      </c>
+      <c r="J21" s="17">
+        <v>1</v>
+      </c>
+      <c r="K21" s="17">
+        <v>0</v>
+      </c>
+      <c r="L21" s="18">
+        <v>0</v>
+      </c>
+      <c r="M21" s="17">
+        <v>99</v>
+      </c>
+      <c r="N21" s="18">
+        <v>1</v>
+      </c>
+      <c r="O21" s="17">
+        <v>19125</v>
+      </c>
+      <c r="P21" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="17"/>
+      <c r="R21" s="17"/>
+      <c r="S21" s="17">
+        <v>0</v>
+      </c>
+      <c r="T21" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="U21" s="19"/>
+      <c r="V21" s="20"/>
+      <c r="W21" s="17">
+        <v>0</v>
+      </c>
+      <c r="X21" s="17">
+        <v>0</v>
+      </c>
+      <c r="Y21" s="17">
+        <v>0</v>
+      </c>
+      <c r="Z21" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:26">
+      <c r="C22" s="14">
+        <v>17</v>
+      </c>
+      <c r="D22" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="E22" s="14">
+        <v>10000101</v>
+      </c>
+      <c r="F22" s="14">
+        <v>0</v>
+      </c>
+      <c r="G22" s="14">
+        <v>3</v>
+      </c>
+      <c r="H22" s="17">
+        <v>1</v>
+      </c>
+      <c r="I22" s="17">
+        <v>0</v>
+      </c>
+      <c r="J22" s="17">
+        <v>1</v>
+      </c>
+      <c r="K22" s="17">
+        <v>0</v>
+      </c>
+      <c r="L22" s="18">
+        <v>0</v>
+      </c>
+      <c r="M22" s="17">
+        <v>99</v>
+      </c>
+      <c r="N22" s="18">
+        <v>1</v>
+      </c>
+      <c r="O22" s="17">
+        <v>19125</v>
+      </c>
+      <c r="P22" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="17"/>
+      <c r="R22" s="17"/>
+      <c r="S22" s="17">
+        <v>0</v>
+      </c>
+      <c r="T22" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="U22" s="19"/>
+      <c r="V22" s="20"/>
+      <c r="W22" s="17">
+        <v>0</v>
+      </c>
+      <c r="X22" s="17">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="17">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:26">
+      <c r="C23" s="14">
+        <v>18</v>
+      </c>
+      <c r="D23" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="E23" s="14">
+        <v>10000101</v>
+      </c>
+      <c r="F23" s="14">
+        <v>0</v>
+      </c>
+      <c r="G23" s="14">
+        <v>3</v>
+      </c>
+      <c r="H23" s="17">
+        <v>1</v>
+      </c>
+      <c r="I23" s="17">
+        <v>0</v>
+      </c>
+      <c r="J23" s="17">
+        <v>1</v>
+      </c>
+      <c r="K23" s="17">
+        <v>0</v>
+      </c>
+      <c r="L23" s="18">
+        <v>0</v>
+      </c>
+      <c r="M23" s="17">
+        <v>99</v>
+      </c>
+      <c r="N23" s="18">
+        <v>1</v>
+      </c>
+      <c r="O23" s="17">
+        <v>19125</v>
+      </c>
+      <c r="P23" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="17"/>
+      <c r="R23" s="17"/>
+      <c r="S23" s="17">
+        <v>0</v>
+      </c>
+      <c r="T23" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="U23" s="19"/>
+      <c r="V23" s="20"/>
+      <c r="W23" s="17">
+        <v>0</v>
+      </c>
+      <c r="X23" s="17">
+        <v>0</v>
+      </c>
+      <c r="Y23" s="17">
+        <v>0</v>
+      </c>
+      <c r="Z23" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:26">
+      <c r="C24" s="14">
+        <v>19</v>
+      </c>
+      <c r="D24" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="E24" s="14">
+        <v>10000101</v>
+      </c>
+      <c r="F24" s="14">
+        <v>0</v>
+      </c>
+      <c r="G24" s="14">
+        <v>3</v>
+      </c>
+      <c r="H24" s="17">
+        <v>1</v>
+      </c>
+      <c r="I24" s="17">
+        <v>0</v>
+      </c>
+      <c r="J24" s="17">
+        <v>1</v>
+      </c>
+      <c r="K24" s="17">
+        <v>0</v>
+      </c>
+      <c r="L24" s="18">
+        <v>0</v>
+      </c>
+      <c r="M24" s="17">
+        <v>99</v>
+      </c>
+      <c r="N24" s="18">
+        <v>1</v>
+      </c>
+      <c r="O24" s="17">
+        <v>19125</v>
+      </c>
+      <c r="P24" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="17"/>
+      <c r="R24" s="17"/>
+      <c r="S24" s="17">
+        <v>0</v>
+      </c>
+      <c r="T24" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="U24" s="19"/>
+      <c r="V24" s="20"/>
+      <c r="W24" s="17">
+        <v>0</v>
+      </c>
+      <c r="X24" s="17">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="17">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:26">
+      <c r="C25" s="14">
+        <v>20</v>
+      </c>
+      <c r="D25" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="E25" s="14">
+        <v>10000101</v>
+      </c>
+      <c r="F25" s="14">
+        <v>0</v>
+      </c>
+      <c r="G25" s="14">
+        <v>3</v>
+      </c>
+      <c r="H25" s="17">
+        <v>1</v>
+      </c>
+      <c r="I25" s="17">
+        <v>0</v>
+      </c>
+      <c r="J25" s="17">
+        <v>1</v>
+      </c>
+      <c r="K25" s="17">
+        <v>0</v>
+      </c>
+      <c r="L25" s="18">
+        <v>0</v>
+      </c>
+      <c r="M25" s="17">
+        <v>99</v>
+      </c>
+      <c r="N25" s="18">
+        <v>1</v>
+      </c>
+      <c r="O25" s="17">
+        <v>19125</v>
+      </c>
+      <c r="P25" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="17"/>
+      <c r="R25" s="17"/>
+      <c r="S25" s="17">
+        <v>0</v>
+      </c>
+      <c r="T25" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="U25" s="19"/>
+      <c r="V25" s="20"/>
+      <c r="W25" s="17">
+        <v>0</v>
+      </c>
+      <c r="X25" s="17">
+        <v>0</v>
+      </c>
+      <c r="Y25" s="17">
+        <v>0</v>
+      </c>
+      <c r="Z25" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:26">
+      <c r="C26" s="14">
+        <v>21</v>
+      </c>
+      <c r="D26" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="E26" s="14">
+        <v>10000101</v>
+      </c>
+      <c r="F26" s="14">
+        <v>0</v>
+      </c>
+      <c r="G26" s="14">
+        <v>3</v>
+      </c>
+      <c r="H26" s="17">
+        <v>1</v>
+      </c>
+      <c r="I26" s="17">
+        <v>0</v>
+      </c>
+      <c r="J26" s="17">
+        <v>1</v>
+      </c>
+      <c r="K26" s="17">
+        <v>0</v>
+      </c>
+      <c r="L26" s="18">
+        <v>0</v>
+      </c>
+      <c r="M26" s="17">
+        <v>99</v>
+      </c>
+      <c r="N26" s="18">
+        <v>1</v>
+      </c>
+      <c r="O26" s="17">
+        <v>19125</v>
+      </c>
+      <c r="P26" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="17"/>
+      <c r="R26" s="17"/>
+      <c r="S26" s="17">
+        <v>0</v>
+      </c>
+      <c r="T26" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="U26" s="19"/>
+      <c r="V26" s="20"/>
+      <c r="W26" s="17">
+        <v>0</v>
+      </c>
+      <c r="X26" s="17">
+        <v>0</v>
+      </c>
+      <c r="Y26" s="17">
+        <v>0</v>
+      </c>
+      <c r="Z26" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:26">
+      <c r="C27" s="14">
+        <v>22</v>
+      </c>
+      <c r="D27" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="E27" s="14">
+        <v>10000101</v>
+      </c>
+      <c r="F27" s="14">
+        <v>0</v>
+      </c>
+      <c r="G27" s="14">
+        <v>3</v>
+      </c>
+      <c r="H27" s="17">
+        <v>1</v>
+      </c>
+      <c r="I27" s="17">
+        <v>0</v>
+      </c>
+      <c r="J27" s="17">
+        <v>1</v>
+      </c>
+      <c r="K27" s="17">
+        <v>0</v>
+      </c>
+      <c r="L27" s="18">
+        <v>0</v>
+      </c>
+      <c r="M27" s="17">
+        <v>99</v>
+      </c>
+      <c r="N27" s="18">
+        <v>1</v>
+      </c>
+      <c r="O27" s="17">
+        <v>19125</v>
+      </c>
+      <c r="P27" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="17"/>
+      <c r="R27" s="17"/>
+      <c r="S27" s="17">
+        <v>0</v>
+      </c>
+      <c r="T27" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="U27" s="19"/>
+      <c r="V27" s="20"/>
+      <c r="W27" s="17">
+        <v>0</v>
+      </c>
+      <c r="X27" s="17">
+        <v>0</v>
+      </c>
+      <c r="Y27" s="17">
+        <v>0</v>
+      </c>
+      <c r="Z27" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:26">
+      <c r="C28" s="14">
+        <v>23</v>
+      </c>
+      <c r="D28" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="E28" s="14">
+        <v>10000101</v>
+      </c>
+      <c r="F28" s="14">
+        <v>0</v>
+      </c>
+      <c r="G28" s="14">
+        <v>3</v>
+      </c>
+      <c r="H28" s="17">
+        <v>1</v>
+      </c>
+      <c r="I28" s="17">
+        <v>0</v>
+      </c>
+      <c r="J28" s="17">
+        <v>1</v>
+      </c>
+      <c r="K28" s="17">
+        <v>0</v>
+      </c>
+      <c r="L28" s="18">
+        <v>0</v>
+      </c>
+      <c r="M28" s="17">
+        <v>99</v>
+      </c>
+      <c r="N28" s="18">
+        <v>1</v>
+      </c>
+      <c r="O28" s="17">
+        <v>19125</v>
+      </c>
+      <c r="P28" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="17"/>
+      <c r="R28" s="17"/>
+      <c r="S28" s="17">
+        <v>0</v>
+      </c>
+      <c r="T28" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="U28" s="19"/>
+      <c r="V28" s="20"/>
+      <c r="W28" s="17">
+        <v>0</v>
+      </c>
+      <c r="X28" s="17">
+        <v>0</v>
+      </c>
+      <c r="Y28" s="17">
+        <v>0</v>
+      </c>
+      <c r="Z28" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:26">
+      <c r="C29" s="14">
+        <v>24</v>
+      </c>
+      <c r="D29" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="E29" s="14">
+        <v>10000101</v>
+      </c>
+      <c r="F29" s="14">
+        <v>0</v>
+      </c>
+      <c r="G29" s="14">
+        <v>3</v>
+      </c>
+      <c r="H29" s="17">
+        <v>1</v>
+      </c>
+      <c r="I29" s="17">
+        <v>0</v>
+      </c>
+      <c r="J29" s="17">
+        <v>1</v>
+      </c>
+      <c r="K29" s="17">
+        <v>0</v>
+      </c>
+      <c r="L29" s="18">
+        <v>0</v>
+      </c>
+      <c r="M29" s="17">
+        <v>99</v>
+      </c>
+      <c r="N29" s="18">
+        <v>1</v>
+      </c>
+      <c r="O29" s="17">
+        <v>19125</v>
+      </c>
+      <c r="P29" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="17"/>
+      <c r="R29" s="17"/>
+      <c r="S29" s="17">
+        <v>0</v>
+      </c>
+      <c r="T29" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="U29" s="19"/>
+      <c r="V29" s="20"/>
+      <c r="W29" s="17">
+        <v>0</v>
+      </c>
+      <c r="X29" s="17">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="17">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:26">
+      <c r="C30" s="14">
+        <v>25</v>
+      </c>
+      <c r="D30" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="E30" s="14">
+        <v>10000101</v>
+      </c>
+      <c r="F30" s="14">
+        <v>0</v>
+      </c>
+      <c r="G30" s="14">
+        <v>3</v>
+      </c>
+      <c r="H30" s="17">
+        <v>1</v>
+      </c>
+      <c r="I30" s="17">
+        <v>0</v>
+      </c>
+      <c r="J30" s="17">
+        <v>1</v>
+      </c>
+      <c r="K30" s="17">
+        <v>0</v>
+      </c>
+      <c r="L30" s="18">
+        <v>0</v>
+      </c>
+      <c r="M30" s="17">
+        <v>99</v>
+      </c>
+      <c r="N30" s="18">
+        <v>1</v>
+      </c>
+      <c r="O30" s="17">
+        <v>19125</v>
+      </c>
+      <c r="P30" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="17"/>
+      <c r="R30" s="17"/>
+      <c r="S30" s="17">
+        <v>0</v>
+      </c>
+      <c r="T30" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="U30" s="19"/>
+      <c r="V30" s="20"/>
+      <c r="W30" s="17">
+        <v>0</v>
+      </c>
+      <c r="X30" s="17">
+        <v>0</v>
+      </c>
+      <c r="Y30" s="17">
+        <v>0</v>
+      </c>
+      <c r="Z30" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:26">
+      <c r="C31" s="14">
+        <v>26</v>
+      </c>
+      <c r="D31" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="E31" s="14">
+        <v>10000101</v>
+      </c>
+      <c r="F31" s="14">
+        <v>0</v>
+      </c>
+      <c r="G31" s="14">
+        <v>3</v>
+      </c>
+      <c r="H31" s="17">
+        <v>1</v>
+      </c>
+      <c r="I31" s="17">
+        <v>0</v>
+      </c>
+      <c r="J31" s="17">
+        <v>1</v>
+      </c>
+      <c r="K31" s="17">
+        <v>0</v>
+      </c>
+      <c r="L31" s="18">
+        <v>0</v>
+      </c>
+      <c r="M31" s="17">
+        <v>99</v>
+      </c>
+      <c r="N31" s="18">
+        <v>1</v>
+      </c>
+      <c r="O31" s="17">
+        <v>19125</v>
+      </c>
+      <c r="P31" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="17"/>
+      <c r="R31" s="17"/>
+      <c r="S31" s="17">
+        <v>0</v>
+      </c>
+      <c r="T31" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="U31" s="19"/>
+      <c r="V31" s="20"/>
+      <c r="W31" s="17">
+        <v>0</v>
+      </c>
+      <c r="X31" s="17">
+        <v>0</v>
+      </c>
+      <c r="Y31" s="17">
+        <v>0</v>
+      </c>
+      <c r="Z31" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:26">
+      <c r="C32" s="14"/>
+      <c r="D32" s="14"/>
+      <c r="E32" s="14"/>
+      <c r="F32" s="14"/>
+      <c r="G32" s="14"/>
+      <c r="H32" s="17"/>
+      <c r="I32" s="17"/>
+      <c r="J32" s="17"/>
+      <c r="K32" s="17"/>
+      <c r="L32" s="18"/>
+      <c r="M32" s="17"/>
+      <c r="N32" s="18"/>
+      <c r="O32" s="17"/>
+      <c r="P32" s="8"/>
+      <c r="Q32" s="17"/>
+      <c r="R32" s="17"/>
+      <c r="S32" s="17"/>
+      <c r="T32" s="18"/>
+      <c r="U32" s="19"/>
+      <c r="V32" s="20"/>
+      <c r="W32" s="17"/>
+      <c r="X32" s="17"/>
+      <c r="Y32" s="17"/>
+      <c r="Z32" s="17"/>
+    </row>
+    <row r="33" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:26">
+      <c r="C33" s="14"/>
+      <c r="D33" s="14"/>
+      <c r="E33" s="14"/>
+      <c r="F33" s="14"/>
+      <c r="G33" s="14"/>
+      <c r="H33" s="17"/>
+      <c r="I33" s="17"/>
+      <c r="J33" s="17"/>
+      <c r="K33" s="17"/>
+      <c r="L33" s="18"/>
+      <c r="M33" s="17"/>
+      <c r="N33" s="18"/>
+      <c r="O33" s="17"/>
+      <c r="P33" s="8"/>
+      <c r="Q33" s="17"/>
+      <c r="R33" s="17"/>
+      <c r="S33" s="17"/>
+      <c r="T33" s="18"/>
+      <c r="U33" s="19"/>
+      <c r="V33" s="20"/>
+      <c r="W33" s="17"/>
+      <c r="X33" s="17"/>
+      <c r="Y33" s="17"/>
+      <c r="Z33" s="17"/>
+    </row>
+    <row r="34" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:26">
+      <c r="C34" s="14"/>
+      <c r="D34" s="14"/>
+      <c r="E34" s="14"/>
+      <c r="F34" s="14"/>
+      <c r="G34" s="14"/>
+      <c r="H34" s="17"/>
+      <c r="I34" s="17"/>
+      <c r="J34" s="17"/>
+      <c r="K34" s="17"/>
+      <c r="L34" s="18"/>
+      <c r="M34" s="17"/>
+      <c r="N34" s="18"/>
+      <c r="O34" s="17"/>
+      <c r="P34" s="8"/>
+      <c r="Q34" s="17"/>
+      <c r="R34" s="17"/>
+      <c r="S34" s="17"/>
+      <c r="T34" s="18"/>
+      <c r="U34" s="19"/>
+      <c r="V34" s="20"/>
+      <c r="W34" s="17"/>
+      <c r="X34" s="17"/>
+      <c r="Y34" s="17"/>
+      <c r="Z34" s="17"/>
+    </row>
+    <row r="35" spans="3:26">
+      <c r="C35" s="14"/>
+      <c r="D35" s="14"/>
+      <c r="E35" s="14"/>
+      <c r="F35" s="14"/>
+      <c r="G35" s="14"/>
+    </row>
+    <row r="36" spans="3:26">
+      <c r="C36" s="14"/>
+      <c r="D36" s="14"/>
+      <c r="E36" s="14"/>
+      <c r="F36" s="14"/>
+      <c r="G36" s="14"/>
+    </row>
+    <row r="37" spans="3:26">
+      <c r="C37" s="14"/>
+      <c r="D37" s="14"/>
+      <c r="E37" s="14"/>
+      <c r="F37" s="14"/>
+      <c r="G37" s="14"/>
+    </row>
+    <row r="38" spans="3:26">
+      <c r="C38" s="14"/>
+      <c r="D38" s="14"/>
+      <c r="E38" s="14"/>
+      <c r="F38" s="14"/>
+      <c r="G38" s="14"/>
+    </row>
+    <row r="39" spans="3:26">
+      <c r="C39" s="14"/>
+      <c r="D39" s="14"/>
+      <c r="E39" s="14"/>
+      <c r="F39" s="14"/>
+      <c r="G39" s="14"/>
+    </row>
+    <row r="40" spans="3:26">
+      <c r="C40" s="14"/>
+      <c r="D40" s="14"/>
+      <c r="E40" s="14"/>
+      <c r="F40" s="14"/>
+      <c r="G40" s="14"/>
+    </row>
+    <row r="41" spans="3:26">
+      <c r="C41" s="14"/>
+      <c r="D41" s="14"/>
+      <c r="E41" s="14"/>
+      <c r="F41" s="14"/>
+      <c r="G41" s="14"/>
+    </row>
+    <row r="42" spans="3:26">
+      <c r="C42" s="14"/>
+      <c r="D42" s="14"/>
+      <c r="E42" s="14"/>
+      <c r="F42" s="14"/>
+      <c r="G42" s="14"/>
+    </row>
+    <row r="43" spans="3:26">
+      <c r="C43" s="14"/>
+      <c r="D43" s="14"/>
+      <c r="E43" s="14"/>
+      <c r="F43" s="14"/>
+      <c r="G43" s="14"/>
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="R1:R16" etc:filterBottomFollowUsedRange="0">

--- a/Unity/Assets/Config/Excel/ItemConfig.xlsx
+++ b/Unity/Assets/Config/Excel/ItemConfig.xlsx
@@ -218,39 +218,7 @@
       <text/>
     </comment>
     <comment ref="L3" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Administrator:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-此字段是装备时有效
-0:通用
-1:剑
-2:刀
-3:法杖
-4：魔法书
-5：弓箭
-11:布甲
-12:轻甲
-13:重甲
-99:无限制
-101 生肖
-201 晶核
-301 宠物装备</t>
-        </r>
-      </text>
+      <text/>
     </comment>
     <comment ref="N3" authorId="0">
       <text>
@@ -319,54 +287,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S3" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Administrator:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-是否在装备Tips显示
-0显示  1不显示</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="W3" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Administrator:
-0 不是自动使用
-1 自动使用</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="X3" authorId="0">
+    <comment ref="T3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -390,7 +311,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Y3" authorId="0">
+    <comment ref="U3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -413,7 +334,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Z3" authorId="0">
+    <comment ref="V3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -442,7 +363,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="75">
   <si>
     <t xml:space="preserve"> </t>
   </si>
@@ -495,19 +416,7 @@
     <t>道具技能</t>
   </si>
   <si>
-    <t>道具Tips显示技能</t>
-  </si>
-  <si>
-    <t>回收获取物品</t>
-  </si>
-  <si>
     <t>道具描述</t>
-  </si>
-  <si>
-    <t>道具背景描述</t>
-  </si>
-  <si>
-    <t>是否自动使用</t>
   </si>
   <si>
     <t>是否禁止拍卖行上架</t>
@@ -564,36 +473,7 @@
     <t>SkillID</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="0"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>S</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="0"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>killIDIfShow</t>
-    </r>
-  </si>
-  <si>
-    <t>HuiShouGetItem</t>
-  </si>
-  <si>
     <t>ItemDes</t>
-  </si>
-  <si>
-    <t>ItemBlackDes</t>
-  </si>
-  <si>
-    <t>IfAutoUse</t>
   </si>
   <si>
     <t>IfStopPaiMai</t>
@@ -620,9 +500,6 @@
     <t>可以在商人购买商品时使用的货币。</t>
   </si>
   <si>
-    <t>嘿嘿嘿!</t>
-  </si>
-  <si>
     <t>（测试）元宝</t>
   </si>
   <si>
@@ -630,9 +507,6 @@
   </si>
   <si>
     <t>角色经验值,可以提升主角等级哦！</t>
-  </si>
-  <si>
-    <t>好高兴啊，又可以快速成长了!</t>
   </si>
   <si>
     <t>（测试）钻石</t>
@@ -662,19 +536,10 @@
     <t>（测试）坚壁刀</t>
   </si>
   <si>
-    <t>1000019,8</t>
-  </si>
-  <si>
     <t>（测试）唤灵之刀</t>
   </si>
   <si>
-    <t>1000019,13;1000018,1</t>
-  </si>
-  <si>
     <t>（测试）小飞鞋</t>
-  </si>
-  <si>
-    <t>1000019,10</t>
   </si>
   <si>
     <t>（测试）幸运符</t>
@@ -683,46 +548,46 @@
     <t>（测试）抓捕器</t>
   </si>
   <si>
-    <t>荣誉级勋章1级</t>
+    <t>（测试）荣誉级勋章1级</t>
   </si>
   <si>
-    <t>荣誉级勋章2级</t>
+    <t>（测试）荣誉级勋章2级</t>
   </si>
   <si>
-    <t>荣誉级勋章3级</t>
+    <t>（测试）荣誉级勋章3级</t>
   </si>
   <si>
-    <t>荣誉级勋章4级</t>
+    <t>（测试）荣誉级勋章4级</t>
   </si>
   <si>
-    <t>圣战级勋章1级</t>
+    <t>（测试）圣战级勋章1级</t>
   </si>
   <si>
-    <t>圣战级勋章2级</t>
+    <t>（测试）圣战级勋章2级</t>
   </si>
   <si>
-    <t>白虎印</t>
+    <t>（测试）白虎印</t>
   </si>
   <si>
-    <t>朱雀印</t>
+    <t>（测试）朱雀印</t>
   </si>
   <si>
-    <t>青龙印</t>
+    <t>（测试）青龙印</t>
   </si>
   <si>
-    <t>无双勋章</t>
+    <t>（测试）无双勋章</t>
   </si>
   <si>
-    <t>荒古勋章</t>
+    <t>（测试）荒古勋章</t>
   </si>
   <si>
-    <t>星辰勋章</t>
+    <t>（测试）星辰勋章</t>
   </si>
   <si>
-    <t>战神凭证</t>
+    <t>（测试）战神凭证</t>
   </si>
   <si>
-    <t>帝释天勋章</t>
+    <t>（测试）帝释天勋章</t>
   </si>
 </sst>
 </file>
@@ -735,7 +600,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="35">
+  <fonts count="34">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -947,24 +812,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -977,6 +825,17 @@
       <b/>
       <sz val="9"/>
       <name val="Tahoma"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -6054,7 +5913,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -6088,9 +5947,6 @@
     <xf numFmtId="49" fontId="5" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -6108,9 +5964,6 @@
     </xf>
     <xf numFmtId="49" fontId="6" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1562">
@@ -7700,7 +7553,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2">
-    <tableStyle name="MySqlDefault" count="2" xr9:uid="{67121B24-83FB-4E7D-BD55-E68D33E68AAA}">
+    <tableStyle name="MySqlDefault" count="2" xr9:uid="{87960A20-1E1F-421C-ABD8-52D850C6FBDC}">
       <tableStyleElement type="wholeTable" dxfId="1"/>
       <tableStyleElement type="headerRow" dxfId="0"/>
     </tableStyle>
@@ -8000,7 +7853,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:Z43"/>
+  <dimension ref="C1:V43"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="2" width="10.875" customWidth="1"/>
@@ -8017,19 +7870,16 @@
     <col min="16" max="16" width="15.5" customWidth="1"/>
     <col min="17" max="17" width="39.625" customWidth="1"/>
     <col min="18" max="18" width="45.375" customWidth="1"/>
-    <col min="19" max="19" width="25.75" customWidth="1"/>
-    <col min="20" max="20" width="33.75" customWidth="1"/>
-    <col min="21" max="21" width="79.875" customWidth="1"/>
-    <col min="22" max="22" width="43.125" customWidth="1"/>
-    <col min="23" max="26" width="15" customWidth="1"/>
+    <col min="19" max="19" width="52.875" customWidth="1"/>
+    <col min="20" max="22" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="3:26">
+    <row r="1" s="1" customFormat="1" spans="3:22">
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" ht="20.1" customHeight="1" spans="3:26">
+    <row r="3" ht="20.1" customHeight="1" spans="3:22">
       <c r="C3" s="3" t="s">
         <v>1</v>
       </c>
@@ -8081,185 +7931,149 @@
       <c r="S3" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="T3" s="4" t="s">
+      <c r="T3" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="U3" s="4" t="s">
+      <c r="U3" s="5" t="s">
         <v>19</v>
       </c>
       <c r="V3" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="W3" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="X3" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="Y3" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="Z3" s="5" t="s">
-        <v>24</v>
-      </c>
     </row>
-    <row r="4" ht="20.1" customHeight="1" spans="3:26">
+    <row r="4" ht="20.1" customHeight="1" spans="3:22">
       <c r="C4" s="3" t="s">
         <v>1</v>
       </c>
       <c r="D4" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="I4" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="J4" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="K4" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="L4" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="I4" s="6" t="s">
+      <c r="M4" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="J4" s="6" t="s">
+      <c r="N4" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="K4" s="6" t="s">
+      <c r="O4" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L4" s="6" t="s">
+      <c r="P4" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="M4" s="6" t="s">
+      <c r="Q4" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="N4" s="6" t="s">
+      <c r="R4" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="O4" s="6" t="s">
+      <c r="S4" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="P4" s="6" t="s">
+      <c r="T4" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="Q4" s="6" t="s">
+      <c r="U4" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="R4" s="6" t="s">
+      <c r="V4" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="S4" s="6" t="s">
+    </row>
+    <row r="5" ht="20.1" customHeight="1" spans="3:22">
+      <c r="C5" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="T4" s="6" t="s">
+      <c r="D5" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="U4" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="V4" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="W4" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="X4" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="Y4" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="Z4" s="5" t="s">
-        <v>47</v>
+      <c r="E5" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="L5" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="M5" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="N5" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="O5" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="P5" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q5" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="R5" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="S5" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="T5" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="U5" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="V5" s="5" t="s">
+        <v>40</v>
       </c>
     </row>
-    <row r="5" ht="20.1" customHeight="1" spans="3:26">
-      <c r="C5" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="L5" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="M5" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="N5" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="O5" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="P5" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q5" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="R5" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="S5" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="T5" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="U5" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="V5" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="W5" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="X5" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="Y5" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="Z5" s="5" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="6" customFormat="1" ht="20.1" customHeight="1" spans="3:26">
+    <row r="6" customFormat="1" ht="20.1" customHeight="1" spans="3:22">
       <c r="C6" s="7">
         <v>1</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="F6" s="9">
         <v>0</v>
@@ -8300,38 +8114,28 @@
       <c r="R6" s="8">
         <v>0</v>
       </c>
-      <c r="S6" s="8">
-        <v>0</v>
-      </c>
-      <c r="T6" s="11"/>
-      <c r="U6" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="V6" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="W6" s="8">
-        <v>0</v>
-      </c>
-      <c r="X6" s="8">
+      <c r="S6" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="T6" s="8">
         <v>1</v>
       </c>
-      <c r="Y6" s="8">
-        <v>0</v>
-      </c>
-      <c r="Z6" s="8">
+      <c r="U6" s="8">
+        <v>0</v>
+      </c>
+      <c r="V6" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="7" ht="20.1" customHeight="1" spans="3:26">
+    <row r="7" ht="20.1" customHeight="1" spans="3:22">
       <c r="C7" s="7">
         <v>2</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="F7" s="9">
         <v>0</v>
@@ -8372,35 +8176,25 @@
       <c r="R7" s="8">
         <v>0</v>
       </c>
-      <c r="S7" s="8">
-        <v>0</v>
-      </c>
-      <c r="T7" s="11"/>
-      <c r="U7" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="V7" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="W7" s="8">
-        <v>0</v>
-      </c>
-      <c r="X7" s="8">
+      <c r="S7" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="T7" s="8">
         <v>1</v>
       </c>
-      <c r="Y7" s="8">
-        <v>0</v>
-      </c>
-      <c r="Z7" s="8">
+      <c r="U7" s="8">
+        <v>0</v>
+      </c>
+      <c r="V7" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="8" ht="20.1" customHeight="1" spans="3:26">
+    <row r="8" ht="20.1" customHeight="1" spans="3:22">
       <c r="C8" s="7">
         <v>3</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="E8" s="8">
         <v>2</v>
@@ -8444,44 +8238,34 @@
       <c r="R8" s="8">
         <v>0</v>
       </c>
-      <c r="S8" s="8">
-        <v>0</v>
-      </c>
-      <c r="T8" s="11"/>
-      <c r="U8" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="V8" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="W8" s="8">
-        <v>0</v>
-      </c>
-      <c r="X8" s="8">
+      <c r="S8" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="T8" s="8">
         <v>1</v>
       </c>
-      <c r="Y8" s="8">
-        <v>0</v>
-      </c>
-      <c r="Z8" s="8">
+      <c r="U8" s="8">
+        <v>0</v>
+      </c>
+      <c r="V8" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="9" ht="20.1" customHeight="1" spans="3:26">
+    <row r="9" ht="20.1" customHeight="1" spans="3:22">
       <c r="C9" s="7">
         <v>4</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="F9" s="9">
         <v>0</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H9" s="8">
         <v>0</v>
@@ -8516,33 +8300,25 @@
       <c r="R9" s="8">
         <v>0</v>
       </c>
-      <c r="S9" s="8">
-        <v>0</v>
-      </c>
-      <c r="T9" s="11"/>
-      <c r="U9" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="V9" s="13"/>
-      <c r="W9" s="8">
-        <v>0</v>
-      </c>
-      <c r="X9" s="8">
+      <c r="S9" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="T9" s="8">
         <v>1</v>
       </c>
-      <c r="Y9" s="8">
-        <v>0</v>
-      </c>
-      <c r="Z9" s="8">
+      <c r="U9" s="8">
+        <v>0</v>
+      </c>
+      <c r="V9" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="10" ht="20.1" customHeight="1" spans="3:26">
+    <row r="10" ht="20.1" customHeight="1" spans="3:22">
       <c r="C10" s="7">
         <v>5</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="E10" s="8">
         <v>4</v>
@@ -8551,7 +8327,7 @@
         <v>0</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H10" s="8">
         <v>0</v>
@@ -8586,33 +8362,25 @@
       <c r="R10" s="8">
         <v>0</v>
       </c>
-      <c r="S10" s="8">
-        <v>0</v>
-      </c>
-      <c r="T10" s="11"/>
-      <c r="U10" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="V10" s="13"/>
-      <c r="W10" s="8">
-        <v>0</v>
-      </c>
-      <c r="X10" s="8">
+      <c r="S10" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="T10" s="8">
         <v>1</v>
       </c>
-      <c r="Y10" s="8">
-        <v>0</v>
-      </c>
-      <c r="Z10" s="8">
+      <c r="U10" s="8">
+        <v>0</v>
+      </c>
+      <c r="V10" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="11" ht="20.1" customHeight="1" spans="3:26">
+    <row r="11" ht="20.1" customHeight="1" spans="3:22">
       <c r="C11" s="7">
         <v>6</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="E11" s="8">
         <v>5</v>
@@ -8621,7 +8389,7 @@
         <v>0</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H11" s="8">
         <v>0</v>
@@ -8656,1487 +8424,1267 @@
       <c r="R11" s="8">
         <v>0</v>
       </c>
-      <c r="S11" s="8">
-        <v>0</v>
-      </c>
-      <c r="T11" s="11"/>
-      <c r="U11" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="V11" s="13"/>
-      <c r="W11" s="8">
-        <v>0</v>
-      </c>
-      <c r="X11" s="8">
+      <c r="S11" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="T11" s="8">
         <v>1</v>
       </c>
-      <c r="Y11" s="8">
-        <v>0</v>
-      </c>
-      <c r="Z11" s="8">
+      <c r="U11" s="8">
+        <v>0</v>
+      </c>
+      <c r="V11" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="12" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:26">
+    <row r="12" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:22">
       <c r="C12" s="7">
         <v>7</v>
       </c>
-      <c r="D12" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="E12" s="14">
+      <c r="D12" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="E12" s="13">
         <v>10000101</v>
       </c>
-      <c r="F12" s="15">
+      <c r="F12" s="14">
         <v>15410003</v>
       </c>
-      <c r="G12" s="16">
+      <c r="G12" s="15">
         <v>3</v>
       </c>
-      <c r="H12" s="17">
+      <c r="H12" s="16">
         <v>40</v>
       </c>
-      <c r="I12" s="17">
-        <v>0</v>
-      </c>
-      <c r="J12" s="17">
+      <c r="I12" s="16">
+        <v>0</v>
+      </c>
+      <c r="J12" s="16">
         <v>3</v>
       </c>
-      <c r="K12" s="17">
+      <c r="K12" s="16">
         <v>1</v>
       </c>
-      <c r="L12" s="18">
+      <c r="L12" s="17">
         <v>2</v>
       </c>
-      <c r="M12" s="17">
+      <c r="M12" s="16">
         <v>1</v>
       </c>
-      <c r="N12" s="18">
+      <c r="N12" s="17">
         <v>1</v>
       </c>
-      <c r="O12" s="17">
+      <c r="O12" s="16">
         <v>15375</v>
       </c>
       <c r="P12" s="8">
         <v>0</v>
       </c>
-      <c r="Q12" s="17"/>
-      <c r="R12" s="17"/>
-      <c r="S12" s="17">
-        <v>0</v>
-      </c>
-      <c r="T12" s="18" t="s">
-        <v>67</v>
-      </c>
-      <c r="U12" s="19"/>
-      <c r="V12" s="20"/>
-      <c r="W12" s="17">
-        <v>0</v>
-      </c>
-      <c r="X12" s="17">
-        <v>0</v>
-      </c>
-      <c r="Y12" s="17">
-        <v>0</v>
-      </c>
-      <c r="Z12" s="17">
+      <c r="Q12" s="16"/>
+      <c r="R12" s="16"/>
+      <c r="S12" s="18"/>
+      <c r="T12" s="16">
+        <v>0</v>
+      </c>
+      <c r="U12" s="16">
+        <v>0</v>
+      </c>
+      <c r="V12" s="16">
         <v>0</v>
       </c>
     </row>
-    <row r="13" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:26">
+    <row r="13" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:22">
       <c r="C13" s="7">
         <v>8</v>
       </c>
-      <c r="D13" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="E13" s="14">
+      <c r="D13" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="E13" s="13">
         <v>10000101</v>
       </c>
-      <c r="F13" s="15">
+      <c r="F13" s="14">
         <v>15410004</v>
       </c>
-      <c r="G13" s="16">
+      <c r="G13" s="15">
         <v>4</v>
       </c>
-      <c r="H13" s="17">
+      <c r="H13" s="16">
         <v>40</v>
       </c>
-      <c r="I13" s="17">
-        <v>0</v>
-      </c>
-      <c r="J13" s="17">
+      <c r="I13" s="16">
+        <v>0</v>
+      </c>
+      <c r="J13" s="16">
         <v>3</v>
       </c>
-      <c r="K13" s="17">
+      <c r="K13" s="16">
         <v>1</v>
       </c>
-      <c r="L13" s="18">
+      <c r="L13" s="17">
         <v>2</v>
       </c>
-      <c r="M13" s="17">
+      <c r="M13" s="16">
         <v>1</v>
       </c>
-      <c r="N13" s="18">
+      <c r="N13" s="17">
         <v>1</v>
       </c>
-      <c r="O13" s="17">
+      <c r="O13" s="16">
         <v>18450</v>
       </c>
       <c r="P13" s="8">
         <v>0</v>
       </c>
-      <c r="Q13" s="17"/>
-      <c r="R13" s="17"/>
-      <c r="S13" s="17">
-        <v>0</v>
-      </c>
-      <c r="T13" s="18" t="s">
-        <v>69</v>
-      </c>
-      <c r="U13" s="19"/>
-      <c r="V13" s="20"/>
-      <c r="W13" s="17">
-        <v>0</v>
-      </c>
-      <c r="X13" s="17">
-        <v>0</v>
-      </c>
-      <c r="Y13" s="17">
-        <v>0</v>
-      </c>
-      <c r="Z13" s="17">
+      <c r="Q13" s="16"/>
+      <c r="R13" s="16"/>
+      <c r="S13" s="18"/>
+      <c r="T13" s="16">
+        <v>0</v>
+      </c>
+      <c r="U13" s="16">
+        <v>0</v>
+      </c>
+      <c r="V13" s="16">
         <v>0</v>
       </c>
     </row>
-    <row r="14" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:26">
+    <row r="14" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:22">
       <c r="C14" s="7">
         <v>9</v>
       </c>
-      <c r="D14" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="E14" s="14">
+      <c r="D14" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="E14" s="13">
         <v>10000101</v>
       </c>
-      <c r="F14" s="15">
-        <v>0</v>
-      </c>
-      <c r="G14" s="16">
+      <c r="F14" s="14">
+        <v>0</v>
+      </c>
+      <c r="G14" s="15">
         <v>3</v>
       </c>
-      <c r="H14" s="17">
+      <c r="H14" s="16">
         <v>1</v>
       </c>
-      <c r="I14" s="17">
-        <v>0</v>
-      </c>
-      <c r="J14" s="17">
+      <c r="I14" s="16">
+        <v>0</v>
+      </c>
+      <c r="J14" s="16">
         <v>1</v>
       </c>
-      <c r="K14" s="17">
-        <v>0</v>
-      </c>
-      <c r="L14" s="18">
-        <v>0</v>
-      </c>
-      <c r="M14" s="17">
+      <c r="K14" s="16">
+        <v>0</v>
+      </c>
+      <c r="L14" s="17">
+        <v>0</v>
+      </c>
+      <c r="M14" s="16">
         <v>99</v>
       </c>
-      <c r="N14" s="18">
+      <c r="N14" s="17">
         <v>1</v>
       </c>
-      <c r="O14" s="17">
+      <c r="O14" s="16">
         <v>19125</v>
       </c>
       <c r="P14" s="8">
         <v>0</v>
       </c>
-      <c r="Q14" s="17"/>
-      <c r="R14" s="17"/>
-      <c r="S14" s="17">
-        <v>0</v>
-      </c>
-      <c r="T14" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="U14" s="19"/>
-      <c r="V14" s="20"/>
-      <c r="W14" s="17">
-        <v>0</v>
-      </c>
-      <c r="X14" s="17">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="17">
-        <v>0</v>
-      </c>
-      <c r="Z14" s="17">
+      <c r="Q14" s="16"/>
+      <c r="R14" s="16"/>
+      <c r="S14" s="18"/>
+      <c r="T14" s="16">
+        <v>0</v>
+      </c>
+      <c r="U14" s="16">
+        <v>0</v>
+      </c>
+      <c r="V14" s="16">
         <v>0</v>
       </c>
     </row>
-    <row r="15" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:26">
+    <row r="15" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:22">
       <c r="C15" s="7">
         <v>10</v>
       </c>
-      <c r="D15" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="E15" s="14">
+      <c r="D15" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="E15" s="13">
         <v>10000101</v>
       </c>
-      <c r="F15" s="15">
-        <v>0</v>
-      </c>
-      <c r="G15" s="16">
+      <c r="F15" s="14">
+        <v>0</v>
+      </c>
+      <c r="G15" s="15">
         <v>3</v>
       </c>
-      <c r="H15" s="17">
+      <c r="H15" s="16">
         <v>1</v>
       </c>
-      <c r="I15" s="17">
-        <v>0</v>
-      </c>
-      <c r="J15" s="17">
+      <c r="I15" s="16">
+        <v>0</v>
+      </c>
+      <c r="J15" s="16">
         <v>1</v>
       </c>
-      <c r="K15" s="17">
-        <v>0</v>
-      </c>
-      <c r="L15" s="18">
-        <v>0</v>
-      </c>
-      <c r="M15" s="17">
+      <c r="K15" s="16">
+        <v>0</v>
+      </c>
+      <c r="L15" s="17">
+        <v>0</v>
+      </c>
+      <c r="M15" s="16">
         <v>99</v>
       </c>
-      <c r="N15" s="18">
+      <c r="N15" s="17">
         <v>1</v>
       </c>
-      <c r="O15" s="17">
+      <c r="O15" s="16">
         <v>19125</v>
       </c>
       <c r="P15" s="8">
         <v>0</v>
       </c>
-      <c r="Q15" s="17"/>
-      <c r="R15" s="17"/>
-      <c r="S15" s="17">
-        <v>0</v>
-      </c>
-      <c r="T15" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="U15" s="19"/>
-      <c r="V15" s="20"/>
-      <c r="W15" s="17">
-        <v>0</v>
-      </c>
-      <c r="X15" s="17">
-        <v>0</v>
-      </c>
-      <c r="Y15" s="17">
-        <v>0</v>
-      </c>
-      <c r="Z15" s="17">
+      <c r="Q15" s="16"/>
+      <c r="R15" s="16"/>
+      <c r="S15" s="18"/>
+      <c r="T15" s="16">
+        <v>0</v>
+      </c>
+      <c r="U15" s="16">
+        <v>0</v>
+      </c>
+      <c r="V15" s="16">
         <v>0</v>
       </c>
     </row>
-    <row r="16" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:26">
+    <row r="16" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:22">
       <c r="C16" s="7">
         <v>11</v>
       </c>
-      <c r="D16" s="14" t="s">
+      <c r="D16" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="E16" s="13">
+        <v>10000101</v>
+      </c>
+      <c r="F16" s="14">
+        <v>0</v>
+      </c>
+      <c r="G16" s="15">
+        <v>3</v>
+      </c>
+      <c r="H16" s="16">
+        <v>1</v>
+      </c>
+      <c r="I16" s="16">
+        <v>0</v>
+      </c>
+      <c r="J16" s="16">
+        <v>1</v>
+      </c>
+      <c r="K16" s="16">
+        <v>0</v>
+      </c>
+      <c r="L16" s="17">
+        <v>0</v>
+      </c>
+      <c r="M16" s="16">
+        <v>99</v>
+      </c>
+      <c r="N16" s="17">
+        <v>1</v>
+      </c>
+      <c r="O16" s="16">
+        <v>19125</v>
+      </c>
+      <c r="P16" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="16"/>
+      <c r="R16" s="16"/>
+      <c r="S16" s="18"/>
+      <c r="T16" s="16">
+        <v>0</v>
+      </c>
+      <c r="U16" s="16">
+        <v>0</v>
+      </c>
+      <c r="V16" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:22">
+      <c r="C17" s="13">
+        <v>12</v>
+      </c>
+      <c r="D17" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="E17" s="13">
+        <v>10000101</v>
+      </c>
+      <c r="F17" s="13">
+        <v>0</v>
+      </c>
+      <c r="G17" s="13">
+        <v>3</v>
+      </c>
+      <c r="H17" s="16">
+        <v>1</v>
+      </c>
+      <c r="I17" s="16">
+        <v>0</v>
+      </c>
+      <c r="J17" s="16">
+        <v>1</v>
+      </c>
+      <c r="K17" s="16">
+        <v>0</v>
+      </c>
+      <c r="L17" s="17">
+        <v>0</v>
+      </c>
+      <c r="M17" s="16">
+        <v>99</v>
+      </c>
+      <c r="N17" s="17">
+        <v>1</v>
+      </c>
+      <c r="O17" s="16">
+        <v>19125</v>
+      </c>
+      <c r="P17" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="16"/>
+      <c r="R17" s="16"/>
+      <c r="S17" s="18"/>
+      <c r="T17" s="16">
+        <v>0</v>
+      </c>
+      <c r="U17" s="16">
+        <v>0</v>
+      </c>
+      <c r="V17" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:22">
+      <c r="C18" s="13">
+        <v>13</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="E18" s="13">
+        <v>10000101</v>
+      </c>
+      <c r="F18" s="13">
+        <v>0</v>
+      </c>
+      <c r="G18" s="13">
+        <v>3</v>
+      </c>
+      <c r="H18" s="16">
+        <v>1</v>
+      </c>
+      <c r="I18" s="16">
+        <v>0</v>
+      </c>
+      <c r="J18" s="16">
+        <v>1</v>
+      </c>
+      <c r="K18" s="16">
+        <v>0</v>
+      </c>
+      <c r="L18" s="17">
+        <v>0</v>
+      </c>
+      <c r="M18" s="16">
+        <v>99</v>
+      </c>
+      <c r="N18" s="17">
+        <v>1</v>
+      </c>
+      <c r="O18" s="16">
+        <v>19125</v>
+      </c>
+      <c r="P18" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="16"/>
+      <c r="R18" s="16"/>
+      <c r="S18" s="18"/>
+      <c r="T18" s="16">
+        <v>0</v>
+      </c>
+      <c r="U18" s="16">
+        <v>0</v>
+      </c>
+      <c r="V18" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:22">
+      <c r="C19" s="13">
+        <v>14</v>
+      </c>
+      <c r="D19" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="E19" s="13">
+        <v>10000101</v>
+      </c>
+      <c r="F19" s="13">
+        <v>0</v>
+      </c>
+      <c r="G19" s="13">
+        <v>3</v>
+      </c>
+      <c r="H19" s="16">
+        <v>1</v>
+      </c>
+      <c r="I19" s="16">
+        <v>0</v>
+      </c>
+      <c r="J19" s="16">
+        <v>1</v>
+      </c>
+      <c r="K19" s="16">
+        <v>0</v>
+      </c>
+      <c r="L19" s="17">
+        <v>0</v>
+      </c>
+      <c r="M19" s="16">
+        <v>99</v>
+      </c>
+      <c r="N19" s="17">
+        <v>1</v>
+      </c>
+      <c r="O19" s="16">
+        <v>19125</v>
+      </c>
+      <c r="P19" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="16"/>
+      <c r="R19" s="16"/>
+      <c r="S19" s="18"/>
+      <c r="T19" s="16">
+        <v>0</v>
+      </c>
+      <c r="U19" s="16">
+        <v>0</v>
+      </c>
+      <c r="V19" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:22">
+      <c r="C20" s="13">
+        <v>15</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="E20" s="13">
+        <v>10000101</v>
+      </c>
+      <c r="F20" s="13">
+        <v>0</v>
+      </c>
+      <c r="G20" s="13">
+        <v>3</v>
+      </c>
+      <c r="H20" s="16">
+        <v>1</v>
+      </c>
+      <c r="I20" s="16">
+        <v>0</v>
+      </c>
+      <c r="J20" s="16">
+        <v>1</v>
+      </c>
+      <c r="K20" s="16">
+        <v>0</v>
+      </c>
+      <c r="L20" s="17">
+        <v>0</v>
+      </c>
+      <c r="M20" s="16">
+        <v>99</v>
+      </c>
+      <c r="N20" s="17">
+        <v>1</v>
+      </c>
+      <c r="O20" s="16">
+        <v>19125</v>
+      </c>
+      <c r="P20" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="16"/>
+      <c r="R20" s="16"/>
+      <c r="S20" s="18"/>
+      <c r="T20" s="16">
+        <v>0</v>
+      </c>
+      <c r="U20" s="16">
+        <v>0</v>
+      </c>
+      <c r="V20" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:22">
+      <c r="C21" s="13">
+        <v>16</v>
+      </c>
+      <c r="D21" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="E21" s="13">
+        <v>10000101</v>
+      </c>
+      <c r="F21" s="13">
+        <v>0</v>
+      </c>
+      <c r="G21" s="13">
+        <v>3</v>
+      </c>
+      <c r="H21" s="16">
+        <v>1</v>
+      </c>
+      <c r="I21" s="16">
+        <v>0</v>
+      </c>
+      <c r="J21" s="16">
+        <v>1</v>
+      </c>
+      <c r="K21" s="16">
+        <v>0</v>
+      </c>
+      <c r="L21" s="17">
+        <v>0</v>
+      </c>
+      <c r="M21" s="16">
+        <v>99</v>
+      </c>
+      <c r="N21" s="17">
+        <v>1</v>
+      </c>
+      <c r="O21" s="16">
+        <v>19125</v>
+      </c>
+      <c r="P21" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="16"/>
+      <c r="R21" s="16"/>
+      <c r="S21" s="18"/>
+      <c r="T21" s="16">
+        <v>0</v>
+      </c>
+      <c r="U21" s="16">
+        <v>0</v>
+      </c>
+      <c r="V21" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:22">
+      <c r="C22" s="13">
+        <v>17</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="E22" s="13">
+        <v>10000101</v>
+      </c>
+      <c r="F22" s="13">
+        <v>0</v>
+      </c>
+      <c r="G22" s="13">
+        <v>3</v>
+      </c>
+      <c r="H22" s="16">
+        <v>1</v>
+      </c>
+      <c r="I22" s="16">
+        <v>0</v>
+      </c>
+      <c r="J22" s="16">
+        <v>1</v>
+      </c>
+      <c r="K22" s="16">
+        <v>0</v>
+      </c>
+      <c r="L22" s="17">
+        <v>0</v>
+      </c>
+      <c r="M22" s="16">
+        <v>99</v>
+      </c>
+      <c r="N22" s="17">
+        <v>1</v>
+      </c>
+      <c r="O22" s="16">
+        <v>19125</v>
+      </c>
+      <c r="P22" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="16"/>
+      <c r="R22" s="16"/>
+      <c r="S22" s="18"/>
+      <c r="T22" s="16">
+        <v>0</v>
+      </c>
+      <c r="U22" s="16">
+        <v>0</v>
+      </c>
+      <c r="V22" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:22">
+      <c r="C23" s="13">
+        <v>18</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="E23" s="13">
+        <v>10000101</v>
+      </c>
+      <c r="F23" s="13">
+        <v>0</v>
+      </c>
+      <c r="G23" s="13">
+        <v>3</v>
+      </c>
+      <c r="H23" s="16">
+        <v>1</v>
+      </c>
+      <c r="I23" s="16">
+        <v>0</v>
+      </c>
+      <c r="J23" s="16">
+        <v>1</v>
+      </c>
+      <c r="K23" s="16">
+        <v>0</v>
+      </c>
+      <c r="L23" s="17">
+        <v>0</v>
+      </c>
+      <c r="M23" s="16">
+        <v>99</v>
+      </c>
+      <c r="N23" s="17">
+        <v>1</v>
+      </c>
+      <c r="O23" s="16">
+        <v>19125</v>
+      </c>
+      <c r="P23" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="16"/>
+      <c r="R23" s="16"/>
+      <c r="S23" s="18"/>
+      <c r="T23" s="16">
+        <v>0</v>
+      </c>
+      <c r="U23" s="16">
+        <v>0</v>
+      </c>
+      <c r="V23" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:22">
+      <c r="C24" s="13">
+        <v>19</v>
+      </c>
+      <c r="D24" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="E24" s="13">
+        <v>10000101</v>
+      </c>
+      <c r="F24" s="13">
+        <v>0</v>
+      </c>
+      <c r="G24" s="13">
+        <v>3</v>
+      </c>
+      <c r="H24" s="16">
+        <v>1</v>
+      </c>
+      <c r="I24" s="16">
+        <v>0</v>
+      </c>
+      <c r="J24" s="16">
+        <v>1</v>
+      </c>
+      <c r="K24" s="16">
+        <v>0</v>
+      </c>
+      <c r="L24" s="17">
+        <v>0</v>
+      </c>
+      <c r="M24" s="16">
+        <v>99</v>
+      </c>
+      <c r="N24" s="17">
+        <v>1</v>
+      </c>
+      <c r="O24" s="16">
+        <v>19125</v>
+      </c>
+      <c r="P24" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="16"/>
+      <c r="R24" s="16"/>
+      <c r="S24" s="18"/>
+      <c r="T24" s="16">
+        <v>0</v>
+      </c>
+      <c r="U24" s="16">
+        <v>0</v>
+      </c>
+      <c r="V24" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:22">
+      <c r="C25" s="13">
+        <v>20</v>
+      </c>
+      <c r="D25" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="E25" s="13">
+        <v>10000101</v>
+      </c>
+      <c r="F25" s="13">
+        <v>0</v>
+      </c>
+      <c r="G25" s="13">
+        <v>3</v>
+      </c>
+      <c r="H25" s="16">
+        <v>1</v>
+      </c>
+      <c r="I25" s="16">
+        <v>0</v>
+      </c>
+      <c r="J25" s="16">
+        <v>1</v>
+      </c>
+      <c r="K25" s="16">
+        <v>0</v>
+      </c>
+      <c r="L25" s="17">
+        <v>0</v>
+      </c>
+      <c r="M25" s="16">
+        <v>99</v>
+      </c>
+      <c r="N25" s="17">
+        <v>1</v>
+      </c>
+      <c r="O25" s="16">
+        <v>19125</v>
+      </c>
+      <c r="P25" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="16"/>
+      <c r="R25" s="16"/>
+      <c r="S25" s="18"/>
+      <c r="T25" s="16">
+        <v>0</v>
+      </c>
+      <c r="U25" s="16">
+        <v>0</v>
+      </c>
+      <c r="V25" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:22">
+      <c r="C26" s="13">
+        <v>21</v>
+      </c>
+      <c r="D26" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="E26" s="13">
+        <v>10000101</v>
+      </c>
+      <c r="F26" s="13">
+        <v>0</v>
+      </c>
+      <c r="G26" s="13">
+        <v>3</v>
+      </c>
+      <c r="H26" s="16">
+        <v>1</v>
+      </c>
+      <c r="I26" s="16">
+        <v>0</v>
+      </c>
+      <c r="J26" s="16">
+        <v>1</v>
+      </c>
+      <c r="K26" s="16">
+        <v>0</v>
+      </c>
+      <c r="L26" s="17">
+        <v>0</v>
+      </c>
+      <c r="M26" s="16">
+        <v>99</v>
+      </c>
+      <c r="N26" s="17">
+        <v>1</v>
+      </c>
+      <c r="O26" s="16">
+        <v>19125</v>
+      </c>
+      <c r="P26" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="16"/>
+      <c r="R26" s="16"/>
+      <c r="S26" s="18"/>
+      <c r="T26" s="16">
+        <v>0</v>
+      </c>
+      <c r="U26" s="16">
+        <v>0</v>
+      </c>
+      <c r="V26" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:22">
+      <c r="C27" s="13">
+        <v>22</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="E27" s="13">
+        <v>10000101</v>
+      </c>
+      <c r="F27" s="13">
+        <v>0</v>
+      </c>
+      <c r="G27" s="13">
+        <v>3</v>
+      </c>
+      <c r="H27" s="16">
+        <v>1</v>
+      </c>
+      <c r="I27" s="16">
+        <v>0</v>
+      </c>
+      <c r="J27" s="16">
+        <v>1</v>
+      </c>
+      <c r="K27" s="16">
+        <v>0</v>
+      </c>
+      <c r="L27" s="17">
+        <v>0</v>
+      </c>
+      <c r="M27" s="16">
+        <v>99</v>
+      </c>
+      <c r="N27" s="17">
+        <v>1</v>
+      </c>
+      <c r="O27" s="16">
+        <v>19125</v>
+      </c>
+      <c r="P27" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="16"/>
+      <c r="R27" s="16"/>
+      <c r="S27" s="18"/>
+      <c r="T27" s="16">
+        <v>0</v>
+      </c>
+      <c r="U27" s="16">
+        <v>0</v>
+      </c>
+      <c r="V27" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:22">
+      <c r="C28" s="13">
+        <v>23</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="E28" s="13">
+        <v>10000101</v>
+      </c>
+      <c r="F28" s="13">
+        <v>0</v>
+      </c>
+      <c r="G28" s="13">
+        <v>3</v>
+      </c>
+      <c r="H28" s="16">
+        <v>1</v>
+      </c>
+      <c r="I28" s="16">
+        <v>0</v>
+      </c>
+      <c r="J28" s="16">
+        <v>1</v>
+      </c>
+      <c r="K28" s="16">
+        <v>0</v>
+      </c>
+      <c r="L28" s="17">
+        <v>0</v>
+      </c>
+      <c r="M28" s="16">
+        <v>99</v>
+      </c>
+      <c r="N28" s="17">
+        <v>1</v>
+      </c>
+      <c r="O28" s="16">
+        <v>19125</v>
+      </c>
+      <c r="P28" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="16"/>
+      <c r="R28" s="16"/>
+      <c r="S28" s="18"/>
+      <c r="T28" s="16">
+        <v>0</v>
+      </c>
+      <c r="U28" s="16">
+        <v>0</v>
+      </c>
+      <c r="V28" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:22">
+      <c r="C29" s="13">
+        <v>24</v>
+      </c>
+      <c r="D29" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="E29" s="13">
+        <v>10000101</v>
+      </c>
+      <c r="F29" s="13">
+        <v>0</v>
+      </c>
+      <c r="G29" s="13">
+        <v>3</v>
+      </c>
+      <c r="H29" s="16">
+        <v>1</v>
+      </c>
+      <c r="I29" s="16">
+        <v>0</v>
+      </c>
+      <c r="J29" s="16">
+        <v>1</v>
+      </c>
+      <c r="K29" s="16">
+        <v>0</v>
+      </c>
+      <c r="L29" s="17">
+        <v>0</v>
+      </c>
+      <c r="M29" s="16">
+        <v>99</v>
+      </c>
+      <c r="N29" s="17">
+        <v>1</v>
+      </c>
+      <c r="O29" s="16">
+        <v>19125</v>
+      </c>
+      <c r="P29" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="16"/>
+      <c r="R29" s="16"/>
+      <c r="S29" s="18"/>
+      <c r="T29" s="16">
+        <v>0</v>
+      </c>
+      <c r="U29" s="16">
+        <v>0</v>
+      </c>
+      <c r="V29" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:22">
+      <c r="C30" s="13">
+        <v>25</v>
+      </c>
+      <c r="D30" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="E16" s="14">
+      <c r="E30" s="13">
         <v>10000101</v>
       </c>
-      <c r="F16" s="15">
-        <v>0</v>
-      </c>
-      <c r="G16" s="16">
+      <c r="F30" s="13">
+        <v>0</v>
+      </c>
+      <c r="G30" s="13">
         <v>3</v>
       </c>
-      <c r="H16" s="17">
+      <c r="H30" s="16">
         <v>1</v>
       </c>
-      <c r="I16" s="17">
-        <v>0</v>
-      </c>
-      <c r="J16" s="17">
+      <c r="I30" s="16">
+        <v>0</v>
+      </c>
+      <c r="J30" s="16">
         <v>1</v>
       </c>
-      <c r="K16" s="17">
-        <v>0</v>
-      </c>
-      <c r="L16" s="18">
-        <v>0</v>
-      </c>
-      <c r="M16" s="17">
+      <c r="K30" s="16">
+        <v>0</v>
+      </c>
+      <c r="L30" s="17">
+        <v>0</v>
+      </c>
+      <c r="M30" s="16">
         <v>99</v>
       </c>
-      <c r="N16" s="18">
+      <c r="N30" s="17">
         <v>1</v>
       </c>
-      <c r="O16" s="17">
+      <c r="O30" s="16">
         <v>19125</v>
       </c>
-      <c r="P16" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="17"/>
-      <c r="R16" s="17"/>
-      <c r="S16" s="17">
-        <v>0</v>
-      </c>
-      <c r="T16" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="U16" s="19"/>
-      <c r="V16" s="20"/>
-      <c r="W16" s="17">
-        <v>0</v>
-      </c>
-      <c r="X16" s="17">
-        <v>0</v>
-      </c>
-      <c r="Y16" s="17">
-        <v>0</v>
-      </c>
-      <c r="Z16" s="17">
+      <c r="P30" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="16"/>
+      <c r="R30" s="16"/>
+      <c r="S30" s="18"/>
+      <c r="T30" s="16">
+        <v>0</v>
+      </c>
+      <c r="U30" s="16">
+        <v>0</v>
+      </c>
+      <c r="V30" s="16">
         <v>0</v>
       </c>
     </row>
-    <row r="17" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:26">
-      <c r="C17" s="14">
-        <v>12</v>
-      </c>
-      <c r="D17" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="E17" s="14">
+    <row r="31" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:22">
+      <c r="C31" s="13">
+        <v>26</v>
+      </c>
+      <c r="D31" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="E31" s="13">
         <v>10000101</v>
       </c>
-      <c r="F17" s="14">
-        <v>0</v>
-      </c>
-      <c r="G17" s="14">
+      <c r="F31" s="13">
+        <v>0</v>
+      </c>
+      <c r="G31" s="13">
         <v>3</v>
       </c>
-      <c r="H17" s="17">
+      <c r="H31" s="16">
         <v>1</v>
       </c>
-      <c r="I17" s="17">
-        <v>0</v>
-      </c>
-      <c r="J17" s="17">
+      <c r="I31" s="16">
+        <v>0</v>
+      </c>
+      <c r="J31" s="16">
         <v>1</v>
       </c>
-      <c r="K17" s="17">
-        <v>0</v>
-      </c>
-      <c r="L17" s="18">
-        <v>0</v>
-      </c>
-      <c r="M17" s="17">
+      <c r="K31" s="16">
+        <v>0</v>
+      </c>
+      <c r="L31" s="17">
+        <v>0</v>
+      </c>
+      <c r="M31" s="16">
         <v>99</v>
       </c>
-      <c r="N17" s="18">
+      <c r="N31" s="17">
         <v>1</v>
       </c>
-      <c r="O17" s="17">
+      <c r="O31" s="16">
         <v>19125</v>
       </c>
-      <c r="P17" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="17"/>
-      <c r="R17" s="17"/>
-      <c r="S17" s="17">
-        <v>0</v>
-      </c>
-      <c r="T17" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="U17" s="19"/>
-      <c r="V17" s="20"/>
-      <c r="W17" s="17">
-        <v>0</v>
-      </c>
-      <c r="X17" s="17">
-        <v>0</v>
-      </c>
-      <c r="Y17" s="17">
-        <v>0</v>
-      </c>
-      <c r="Z17" s="17">
+      <c r="P31" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="16"/>
+      <c r="R31" s="16"/>
+      <c r="S31" s="18"/>
+      <c r="T31" s="16">
+        <v>0</v>
+      </c>
+      <c r="U31" s="16">
+        <v>0</v>
+      </c>
+      <c r="V31" s="16">
         <v>0</v>
       </c>
     </row>
-    <row r="18" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:26">
-      <c r="C18" s="14">
-        <v>13</v>
-      </c>
-      <c r="D18" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="E18" s="14">
-        <v>10000101</v>
-      </c>
-      <c r="F18" s="14">
-        <v>0</v>
-      </c>
-      <c r="G18" s="14">
-        <v>3</v>
-      </c>
-      <c r="H18" s="17">
-        <v>1</v>
-      </c>
-      <c r="I18" s="17">
-        <v>0</v>
-      </c>
-      <c r="J18" s="17">
-        <v>1</v>
-      </c>
-      <c r="K18" s="17">
-        <v>0</v>
-      </c>
-      <c r="L18" s="18">
-        <v>0</v>
-      </c>
-      <c r="M18" s="17">
-        <v>99</v>
-      </c>
-      <c r="N18" s="18">
-        <v>1</v>
-      </c>
-      <c r="O18" s="17">
-        <v>19125</v>
-      </c>
-      <c r="P18" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="17"/>
-      <c r="R18" s="17"/>
-      <c r="S18" s="17">
-        <v>0</v>
-      </c>
-      <c r="T18" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="U18" s="19"/>
-      <c r="V18" s="20"/>
-      <c r="W18" s="17">
-        <v>0</v>
-      </c>
-      <c r="X18" s="17">
-        <v>0</v>
-      </c>
-      <c r="Y18" s="17">
-        <v>0</v>
-      </c>
-      <c r="Z18" s="17">
-        <v>0</v>
-      </c>
+    <row r="32" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:22">
+      <c r="C32" s="13"/>
+      <c r="D32" s="13"/>
+      <c r="E32" s="13"/>
+      <c r="F32" s="13"/>
+      <c r="G32" s="13"/>
+      <c r="H32" s="16"/>
+      <c r="I32" s="16"/>
+      <c r="J32" s="16"/>
+      <c r="K32" s="16"/>
+      <c r="L32" s="17"/>
+      <c r="M32" s="16"/>
+      <c r="N32" s="17"/>
+      <c r="O32" s="16"/>
+      <c r="P32" s="8"/>
+      <c r="Q32" s="16"/>
+      <c r="R32" s="16"/>
+      <c r="S32" s="18"/>
+      <c r="T32" s="16"/>
+      <c r="U32" s="16"/>
+      <c r="V32" s="16"/>
     </row>
-    <row r="19" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:26">
-      <c r="C19" s="14">
-        <v>14</v>
-      </c>
-      <c r="D19" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="E19" s="14">
-        <v>10000101</v>
-      </c>
-      <c r="F19" s="14">
-        <v>0</v>
-      </c>
-      <c r="G19" s="14">
-        <v>3</v>
-      </c>
-      <c r="H19" s="17">
-        <v>1</v>
-      </c>
-      <c r="I19" s="17">
-        <v>0</v>
-      </c>
-      <c r="J19" s="17">
-        <v>1</v>
-      </c>
-      <c r="K19" s="17">
-        <v>0</v>
-      </c>
-      <c r="L19" s="18">
-        <v>0</v>
-      </c>
-      <c r="M19" s="17">
-        <v>99</v>
-      </c>
-      <c r="N19" s="18">
-        <v>1</v>
-      </c>
-      <c r="O19" s="17">
-        <v>19125</v>
-      </c>
-      <c r="P19" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q19" s="17"/>
-      <c r="R19" s="17"/>
-      <c r="S19" s="17">
-        <v>0</v>
-      </c>
-      <c r="T19" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="U19" s="19"/>
-      <c r="V19" s="20"/>
-      <c r="W19" s="17">
-        <v>0</v>
-      </c>
-      <c r="X19" s="17">
-        <v>0</v>
-      </c>
-      <c r="Y19" s="17">
-        <v>0</v>
-      </c>
-      <c r="Z19" s="17">
-        <v>0</v>
-      </c>
+    <row r="33" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:22">
+      <c r="C33" s="13"/>
+      <c r="D33" s="13"/>
+      <c r="E33" s="13"/>
+      <c r="F33" s="13"/>
+      <c r="G33" s="13"/>
+      <c r="H33" s="16"/>
+      <c r="I33" s="16"/>
+      <c r="J33" s="16"/>
+      <c r="K33" s="16"/>
+      <c r="L33" s="17"/>
+      <c r="M33" s="16"/>
+      <c r="N33" s="17"/>
+      <c r="O33" s="16"/>
+      <c r="P33" s="8"/>
+      <c r="Q33" s="16"/>
+      <c r="R33" s="16"/>
+      <c r="S33" s="18"/>
+      <c r="T33" s="16"/>
+      <c r="U33" s="16"/>
+      <c r="V33" s="16"/>
     </row>
-    <row r="20" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:26">
-      <c r="C20" s="14">
-        <v>15</v>
-      </c>
-      <c r="D20" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="E20" s="14">
-        <v>10000101</v>
-      </c>
-      <c r="F20" s="14">
-        <v>0</v>
-      </c>
-      <c r="G20" s="14">
-        <v>3</v>
-      </c>
-      <c r="H20" s="17">
-        <v>1</v>
-      </c>
-      <c r="I20" s="17">
-        <v>0</v>
-      </c>
-      <c r="J20" s="17">
-        <v>1</v>
-      </c>
-      <c r="K20" s="17">
-        <v>0</v>
-      </c>
-      <c r="L20" s="18">
-        <v>0</v>
-      </c>
-      <c r="M20" s="17">
-        <v>99</v>
-      </c>
-      <c r="N20" s="18">
-        <v>1</v>
-      </c>
-      <c r="O20" s="17">
-        <v>19125</v>
-      </c>
-      <c r="P20" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="17"/>
-      <c r="R20" s="17"/>
-      <c r="S20" s="17">
-        <v>0</v>
-      </c>
-      <c r="T20" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="U20" s="19"/>
-      <c r="V20" s="20"/>
-      <c r="W20" s="17">
-        <v>0</v>
-      </c>
-      <c r="X20" s="17">
-        <v>0</v>
-      </c>
-      <c r="Y20" s="17">
-        <v>0</v>
-      </c>
-      <c r="Z20" s="17">
-        <v>0</v>
-      </c>
+    <row r="34" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:22">
+      <c r="C34" s="13"/>
+      <c r="D34" s="13"/>
+      <c r="E34" s="13"/>
+      <c r="F34" s="13"/>
+      <c r="G34" s="13"/>
+      <c r="H34" s="16"/>
+      <c r="I34" s="16"/>
+      <c r="J34" s="16"/>
+      <c r="K34" s="16"/>
+      <c r="L34" s="17"/>
+      <c r="M34" s="16"/>
+      <c r="N34" s="17"/>
+      <c r="O34" s="16"/>
+      <c r="P34" s="8"/>
+      <c r="Q34" s="16"/>
+      <c r="R34" s="16"/>
+      <c r="S34" s="18"/>
+      <c r="T34" s="16"/>
+      <c r="U34" s="16"/>
+      <c r="V34" s="16"/>
     </row>
-    <row r="21" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:26">
-      <c r="C21" s="14">
-        <v>16</v>
-      </c>
-      <c r="D21" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="E21" s="14">
-        <v>10000101</v>
-      </c>
-      <c r="F21" s="14">
-        <v>0</v>
-      </c>
-      <c r="G21" s="14">
-        <v>3</v>
-      </c>
-      <c r="H21" s="17">
-        <v>1</v>
-      </c>
-      <c r="I21" s="17">
-        <v>0</v>
-      </c>
-      <c r="J21" s="17">
-        <v>1</v>
-      </c>
-      <c r="K21" s="17">
-        <v>0</v>
-      </c>
-      <c r="L21" s="18">
-        <v>0</v>
-      </c>
-      <c r="M21" s="17">
-        <v>99</v>
-      </c>
-      <c r="N21" s="18">
-        <v>1</v>
-      </c>
-      <c r="O21" s="17">
-        <v>19125</v>
-      </c>
-      <c r="P21" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q21" s="17"/>
-      <c r="R21" s="17"/>
-      <c r="S21" s="17">
-        <v>0</v>
-      </c>
-      <c r="T21" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="U21" s="19"/>
-      <c r="V21" s="20"/>
-      <c r="W21" s="17">
-        <v>0</v>
-      </c>
-      <c r="X21" s="17">
-        <v>0</v>
-      </c>
-      <c r="Y21" s="17">
-        <v>0</v>
-      </c>
-      <c r="Z21" s="17">
-        <v>0</v>
-      </c>
+    <row r="35" spans="3:22">
+      <c r="C35" s="13"/>
+      <c r="D35" s="13"/>
+      <c r="E35" s="13"/>
+      <c r="F35" s="13"/>
+      <c r="G35" s="13"/>
     </row>
-    <row r="22" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:26">
-      <c r="C22" s="14">
-        <v>17</v>
-      </c>
-      <c r="D22" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="E22" s="14">
-        <v>10000101</v>
-      </c>
-      <c r="F22" s="14">
-        <v>0</v>
-      </c>
-      <c r="G22" s="14">
-        <v>3</v>
-      </c>
-      <c r="H22" s="17">
-        <v>1</v>
-      </c>
-      <c r="I22" s="17">
-        <v>0</v>
-      </c>
-      <c r="J22" s="17">
-        <v>1</v>
-      </c>
-      <c r="K22" s="17">
-        <v>0</v>
-      </c>
-      <c r="L22" s="18">
-        <v>0</v>
-      </c>
-      <c r="M22" s="17">
-        <v>99</v>
-      </c>
-      <c r="N22" s="18">
-        <v>1</v>
-      </c>
-      <c r="O22" s="17">
-        <v>19125</v>
-      </c>
-      <c r="P22" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="17"/>
-      <c r="R22" s="17"/>
-      <c r="S22" s="17">
-        <v>0</v>
-      </c>
-      <c r="T22" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="U22" s="19"/>
-      <c r="V22" s="20"/>
-      <c r="W22" s="17">
-        <v>0</v>
-      </c>
-      <c r="X22" s="17">
-        <v>0</v>
-      </c>
-      <c r="Y22" s="17">
-        <v>0</v>
-      </c>
-      <c r="Z22" s="17">
-        <v>0</v>
-      </c>
+    <row r="36" spans="3:22">
+      <c r="C36" s="13"/>
+      <c r="D36" s="13"/>
+      <c r="E36" s="13"/>
+      <c r="F36" s="13"/>
+      <c r="G36" s="13"/>
     </row>
-    <row r="23" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:26">
-      <c r="C23" s="14">
-        <v>18</v>
-      </c>
-      <c r="D23" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="E23" s="14">
-        <v>10000101</v>
-      </c>
-      <c r="F23" s="14">
-        <v>0</v>
-      </c>
-      <c r="G23" s="14">
-        <v>3</v>
-      </c>
-      <c r="H23" s="17">
-        <v>1</v>
-      </c>
-      <c r="I23" s="17">
-        <v>0</v>
-      </c>
-      <c r="J23" s="17">
-        <v>1</v>
-      </c>
-      <c r="K23" s="17">
-        <v>0</v>
-      </c>
-      <c r="L23" s="18">
-        <v>0</v>
-      </c>
-      <c r="M23" s="17">
-        <v>99</v>
-      </c>
-      <c r="N23" s="18">
-        <v>1</v>
-      </c>
-      <c r="O23" s="17">
-        <v>19125</v>
-      </c>
-      <c r="P23" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q23" s="17"/>
-      <c r="R23" s="17"/>
-      <c r="S23" s="17">
-        <v>0</v>
-      </c>
-      <c r="T23" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="U23" s="19"/>
-      <c r="V23" s="20"/>
-      <c r="W23" s="17">
-        <v>0</v>
-      </c>
-      <c r="X23" s="17">
-        <v>0</v>
-      </c>
-      <c r="Y23" s="17">
-        <v>0</v>
-      </c>
-      <c r="Z23" s="17">
-        <v>0</v>
-      </c>
+    <row r="37" spans="3:22">
+      <c r="C37" s="13"/>
+      <c r="D37" s="13"/>
+      <c r="E37" s="13"/>
+      <c r="F37" s="13"/>
+      <c r="G37" s="13"/>
     </row>
-    <row r="24" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:26">
-      <c r="C24" s="14">
-        <v>19</v>
-      </c>
-      <c r="D24" s="14" t="s">
-        <v>80</v>
-      </c>
-      <c r="E24" s="14">
-        <v>10000101</v>
-      </c>
-      <c r="F24" s="14">
-        <v>0</v>
-      </c>
-      <c r="G24" s="14">
-        <v>3</v>
-      </c>
-      <c r="H24" s="17">
-        <v>1</v>
-      </c>
-      <c r="I24" s="17">
-        <v>0</v>
-      </c>
-      <c r="J24" s="17">
-        <v>1</v>
-      </c>
-      <c r="K24" s="17">
-        <v>0</v>
-      </c>
-      <c r="L24" s="18">
-        <v>0</v>
-      </c>
-      <c r="M24" s="17">
-        <v>99</v>
-      </c>
-      <c r="N24" s="18">
-        <v>1</v>
-      </c>
-      <c r="O24" s="17">
-        <v>19125</v>
-      </c>
-      <c r="P24" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q24" s="17"/>
-      <c r="R24" s="17"/>
-      <c r="S24" s="17">
-        <v>0</v>
-      </c>
-      <c r="T24" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="U24" s="19"/>
-      <c r="V24" s="20"/>
-      <c r="W24" s="17">
-        <v>0</v>
-      </c>
-      <c r="X24" s="17">
-        <v>0</v>
-      </c>
-      <c r="Y24" s="17">
-        <v>0</v>
-      </c>
-      <c r="Z24" s="17">
-        <v>0</v>
-      </c>
+    <row r="38" spans="3:22">
+      <c r="C38" s="13"/>
+      <c r="D38" s="13"/>
+      <c r="E38" s="13"/>
+      <c r="F38" s="13"/>
+      <c r="G38" s="13"/>
     </row>
-    <row r="25" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:26">
-      <c r="C25" s="14">
-        <v>20</v>
-      </c>
-      <c r="D25" s="14" t="s">
-        <v>81</v>
-      </c>
-      <c r="E25" s="14">
-        <v>10000101</v>
-      </c>
-      <c r="F25" s="14">
-        <v>0</v>
-      </c>
-      <c r="G25" s="14">
-        <v>3</v>
-      </c>
-      <c r="H25" s="17">
-        <v>1</v>
-      </c>
-      <c r="I25" s="17">
-        <v>0</v>
-      </c>
-      <c r="J25" s="17">
-        <v>1</v>
-      </c>
-      <c r="K25" s="17">
-        <v>0</v>
-      </c>
-      <c r="L25" s="18">
-        <v>0</v>
-      </c>
-      <c r="M25" s="17">
-        <v>99</v>
-      </c>
-      <c r="N25" s="18">
-        <v>1</v>
-      </c>
-      <c r="O25" s="17">
-        <v>19125</v>
-      </c>
-      <c r="P25" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q25" s="17"/>
-      <c r="R25" s="17"/>
-      <c r="S25" s="17">
-        <v>0</v>
-      </c>
-      <c r="T25" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="U25" s="19"/>
-      <c r="V25" s="20"/>
-      <c r="W25" s="17">
-        <v>0</v>
-      </c>
-      <c r="X25" s="17">
-        <v>0</v>
-      </c>
-      <c r="Y25" s="17">
-        <v>0</v>
-      </c>
-      <c r="Z25" s="17">
-        <v>0</v>
-      </c>
+    <row r="39" spans="3:22">
+      <c r="C39" s="13"/>
+      <c r="D39" s="13"/>
+      <c r="E39" s="13"/>
+      <c r="F39" s="13"/>
+      <c r="G39" s="13"/>
     </row>
-    <row r="26" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:26">
-      <c r="C26" s="14">
-        <v>21</v>
-      </c>
-      <c r="D26" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="E26" s="14">
-        <v>10000101</v>
-      </c>
-      <c r="F26" s="14">
-        <v>0</v>
-      </c>
-      <c r="G26" s="14">
-        <v>3</v>
-      </c>
-      <c r="H26" s="17">
-        <v>1</v>
-      </c>
-      <c r="I26" s="17">
-        <v>0</v>
-      </c>
-      <c r="J26" s="17">
-        <v>1</v>
-      </c>
-      <c r="K26" s="17">
-        <v>0</v>
-      </c>
-      <c r="L26" s="18">
-        <v>0</v>
-      </c>
-      <c r="M26" s="17">
-        <v>99</v>
-      </c>
-      <c r="N26" s="18">
-        <v>1</v>
-      </c>
-      <c r="O26" s="17">
-        <v>19125</v>
-      </c>
-      <c r="P26" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q26" s="17"/>
-      <c r="R26" s="17"/>
-      <c r="S26" s="17">
-        <v>0</v>
-      </c>
-      <c r="T26" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="U26" s="19"/>
-      <c r="V26" s="20"/>
-      <c r="W26" s="17">
-        <v>0</v>
-      </c>
-      <c r="X26" s="17">
-        <v>0</v>
-      </c>
-      <c r="Y26" s="17">
-        <v>0</v>
-      </c>
-      <c r="Z26" s="17">
-        <v>0</v>
-      </c>
+    <row r="40" spans="3:22">
+      <c r="C40" s="13"/>
+      <c r="D40" s="13"/>
+      <c r="E40" s="13"/>
+      <c r="F40" s="13"/>
+      <c r="G40" s="13"/>
     </row>
-    <row r="27" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:26">
-      <c r="C27" s="14">
-        <v>22</v>
-      </c>
-      <c r="D27" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="E27" s="14">
-        <v>10000101</v>
-      </c>
-      <c r="F27" s="14">
-        <v>0</v>
-      </c>
-      <c r="G27" s="14">
-        <v>3</v>
-      </c>
-      <c r="H27" s="17">
-        <v>1</v>
-      </c>
-      <c r="I27" s="17">
-        <v>0</v>
-      </c>
-      <c r="J27" s="17">
-        <v>1</v>
-      </c>
-      <c r="K27" s="17">
-        <v>0</v>
-      </c>
-      <c r="L27" s="18">
-        <v>0</v>
-      </c>
-      <c r="M27" s="17">
-        <v>99</v>
-      </c>
-      <c r="N27" s="18">
-        <v>1</v>
-      </c>
-      <c r="O27" s="17">
-        <v>19125</v>
-      </c>
-      <c r="P27" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q27" s="17"/>
-      <c r="R27" s="17"/>
-      <c r="S27" s="17">
-        <v>0</v>
-      </c>
-      <c r="T27" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="U27" s="19"/>
-      <c r="V27" s="20"/>
-      <c r="W27" s="17">
-        <v>0</v>
-      </c>
-      <c r="X27" s="17">
-        <v>0</v>
-      </c>
-      <c r="Y27" s="17">
-        <v>0</v>
-      </c>
-      <c r="Z27" s="17">
-        <v>0</v>
-      </c>
+    <row r="41" spans="3:22">
+      <c r="C41" s="13"/>
+      <c r="D41" s="13"/>
+      <c r="E41" s="13"/>
+      <c r="F41" s="13"/>
+      <c r="G41" s="13"/>
     </row>
-    <row r="28" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:26">
-      <c r="C28" s="14">
-        <v>23</v>
-      </c>
-      <c r="D28" s="14" t="s">
-        <v>84</v>
-      </c>
-      <c r="E28" s="14">
-        <v>10000101</v>
-      </c>
-      <c r="F28" s="14">
-        <v>0</v>
-      </c>
-      <c r="G28" s="14">
-        <v>3</v>
-      </c>
-      <c r="H28" s="17">
-        <v>1</v>
-      </c>
-      <c r="I28" s="17">
-        <v>0</v>
-      </c>
-      <c r="J28" s="17">
-        <v>1</v>
-      </c>
-      <c r="K28" s="17">
-        <v>0</v>
-      </c>
-      <c r="L28" s="18">
-        <v>0</v>
-      </c>
-      <c r="M28" s="17">
-        <v>99</v>
-      </c>
-      <c r="N28" s="18">
-        <v>1</v>
-      </c>
-      <c r="O28" s="17">
-        <v>19125</v>
-      </c>
-      <c r="P28" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q28" s="17"/>
-      <c r="R28" s="17"/>
-      <c r="S28" s="17">
-        <v>0</v>
-      </c>
-      <c r="T28" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="U28" s="19"/>
-      <c r="V28" s="20"/>
-      <c r="W28" s="17">
-        <v>0</v>
-      </c>
-      <c r="X28" s="17">
-        <v>0</v>
-      </c>
-      <c r="Y28" s="17">
-        <v>0</v>
-      </c>
-      <c r="Z28" s="17">
-        <v>0</v>
-      </c>
+    <row r="42" spans="3:22">
+      <c r="C42" s="13"/>
+      <c r="D42" s="13"/>
+      <c r="E42" s="13"/>
+      <c r="F42" s="13"/>
+      <c r="G42" s="13"/>
     </row>
-    <row r="29" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:26">
-      <c r="C29" s="14">
-        <v>24</v>
-      </c>
-      <c r="D29" s="14" t="s">
-        <v>85</v>
-      </c>
-      <c r="E29" s="14">
-        <v>10000101</v>
-      </c>
-      <c r="F29" s="14">
-        <v>0</v>
-      </c>
-      <c r="G29" s="14">
-        <v>3</v>
-      </c>
-      <c r="H29" s="17">
-        <v>1</v>
-      </c>
-      <c r="I29" s="17">
-        <v>0</v>
-      </c>
-      <c r="J29" s="17">
-        <v>1</v>
-      </c>
-      <c r="K29" s="17">
-        <v>0</v>
-      </c>
-      <c r="L29" s="18">
-        <v>0</v>
-      </c>
-      <c r="M29" s="17">
-        <v>99</v>
-      </c>
-      <c r="N29" s="18">
-        <v>1</v>
-      </c>
-      <c r="O29" s="17">
-        <v>19125</v>
-      </c>
-      <c r="P29" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q29" s="17"/>
-      <c r="R29" s="17"/>
-      <c r="S29" s="17">
-        <v>0</v>
-      </c>
-      <c r="T29" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="U29" s="19"/>
-      <c r="V29" s="20"/>
-      <c r="W29" s="17">
-        <v>0</v>
-      </c>
-      <c r="X29" s="17">
-        <v>0</v>
-      </c>
-      <c r="Y29" s="17">
-        <v>0</v>
-      </c>
-      <c r="Z29" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:26">
-      <c r="C30" s="14">
-        <v>25</v>
-      </c>
-      <c r="D30" s="14" t="s">
-        <v>86</v>
-      </c>
-      <c r="E30" s="14">
-        <v>10000101</v>
-      </c>
-      <c r="F30" s="14">
-        <v>0</v>
-      </c>
-      <c r="G30" s="14">
-        <v>3</v>
-      </c>
-      <c r="H30" s="17">
-        <v>1</v>
-      </c>
-      <c r="I30" s="17">
-        <v>0</v>
-      </c>
-      <c r="J30" s="17">
-        <v>1</v>
-      </c>
-      <c r="K30" s="17">
-        <v>0</v>
-      </c>
-      <c r="L30" s="18">
-        <v>0</v>
-      </c>
-      <c r="M30" s="17">
-        <v>99</v>
-      </c>
-      <c r="N30" s="18">
-        <v>1</v>
-      </c>
-      <c r="O30" s="17">
-        <v>19125</v>
-      </c>
-      <c r="P30" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q30" s="17"/>
-      <c r="R30" s="17"/>
-      <c r="S30" s="17">
-        <v>0</v>
-      </c>
-      <c r="T30" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="U30" s="19"/>
-      <c r="V30" s="20"/>
-      <c r="W30" s="17">
-        <v>0</v>
-      </c>
-      <c r="X30" s="17">
-        <v>0</v>
-      </c>
-      <c r="Y30" s="17">
-        <v>0</v>
-      </c>
-      <c r="Z30" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:26">
-      <c r="C31" s="14">
-        <v>26</v>
-      </c>
-      <c r="D31" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="E31" s="14">
-        <v>10000101</v>
-      </c>
-      <c r="F31" s="14">
-        <v>0</v>
-      </c>
-      <c r="G31" s="14">
-        <v>3</v>
-      </c>
-      <c r="H31" s="17">
-        <v>1</v>
-      </c>
-      <c r="I31" s="17">
-        <v>0</v>
-      </c>
-      <c r="J31" s="17">
-        <v>1</v>
-      </c>
-      <c r="K31" s="17">
-        <v>0</v>
-      </c>
-      <c r="L31" s="18">
-        <v>0</v>
-      </c>
-      <c r="M31" s="17">
-        <v>99</v>
-      </c>
-      <c r="N31" s="18">
-        <v>1</v>
-      </c>
-      <c r="O31" s="17">
-        <v>19125</v>
-      </c>
-      <c r="P31" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q31" s="17"/>
-      <c r="R31" s="17"/>
-      <c r="S31" s="17">
-        <v>0</v>
-      </c>
-      <c r="T31" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="U31" s="19"/>
-      <c r="V31" s="20"/>
-      <c r="W31" s="17">
-        <v>0</v>
-      </c>
-      <c r="X31" s="17">
-        <v>0</v>
-      </c>
-      <c r="Y31" s="17">
-        <v>0</v>
-      </c>
-      <c r="Z31" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:26">
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="17"/>
-      <c r="I32" s="17"/>
-      <c r="J32" s="17"/>
-      <c r="K32" s="17"/>
-      <c r="L32" s="18"/>
-      <c r="M32" s="17"/>
-      <c r="N32" s="18"/>
-      <c r="O32" s="17"/>
-      <c r="P32" s="8"/>
-      <c r="Q32" s="17"/>
-      <c r="R32" s="17"/>
-      <c r="S32" s="17"/>
-      <c r="T32" s="18"/>
-      <c r="U32" s="19"/>
-      <c r="V32" s="20"/>
-      <c r="W32" s="17"/>
-      <c r="X32" s="17"/>
-      <c r="Y32" s="17"/>
-      <c r="Z32" s="17"/>
-    </row>
-    <row r="33" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:26">
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="17"/>
-      <c r="I33" s="17"/>
-      <c r="J33" s="17"/>
-      <c r="K33" s="17"/>
-      <c r="L33" s="18"/>
-      <c r="M33" s="17"/>
-      <c r="N33" s="18"/>
-      <c r="O33" s="17"/>
-      <c r="P33" s="8"/>
-      <c r="Q33" s="17"/>
-      <c r="R33" s="17"/>
-      <c r="S33" s="17"/>
-      <c r="T33" s="18"/>
-      <c r="U33" s="19"/>
-      <c r="V33" s="20"/>
-      <c r="W33" s="17"/>
-      <c r="X33" s="17"/>
-      <c r="Y33" s="17"/>
-      <c r="Z33" s="17"/>
-    </row>
-    <row r="34" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:26">
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="17"/>
-      <c r="I34" s="17"/>
-      <c r="J34" s="17"/>
-      <c r="K34" s="17"/>
-      <c r="L34" s="18"/>
-      <c r="M34" s="17"/>
-      <c r="N34" s="18"/>
-      <c r="O34" s="17"/>
-      <c r="P34" s="8"/>
-      <c r="Q34" s="17"/>
-      <c r="R34" s="17"/>
-      <c r="S34" s="17"/>
-      <c r="T34" s="18"/>
-      <c r="U34" s="19"/>
-      <c r="V34" s="20"/>
-      <c r="W34" s="17"/>
-      <c r="X34" s="17"/>
-      <c r="Y34" s="17"/>
-      <c r="Z34" s="17"/>
-    </row>
-    <row r="35" spans="3:26">
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-    </row>
-    <row r="36" spans="3:26">
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-    </row>
-    <row r="37" spans="3:26">
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
-    </row>
-    <row r="38" spans="3:26">
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
-    </row>
-    <row r="39" spans="3:26">
-      <c r="C39" s="14"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14"/>
-      <c r="G39" s="14"/>
-    </row>
-    <row r="40" spans="3:26">
-      <c r="C40" s="14"/>
-      <c r="D40" s="14"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="14"/>
-    </row>
-    <row r="41" spans="3:26">
-      <c r="C41" s="14"/>
-      <c r="D41" s="14"/>
-      <c r="E41" s="14"/>
-      <c r="F41" s="14"/>
-      <c r="G41" s="14"/>
-    </row>
-    <row r="42" spans="3:26">
-      <c r="C42" s="14"/>
-      <c r="D42" s="14"/>
-      <c r="E42" s="14"/>
-      <c r="F42" s="14"/>
-      <c r="G42" s="14"/>
-    </row>
-    <row r="43" spans="3:26">
-      <c r="C43" s="14"/>
-      <c r="D43" s="14"/>
-      <c r="E43" s="14"/>
-      <c r="F43" s="14"/>
-      <c r="G43" s="14"/>
+    <row r="43" spans="3:22">
+      <c r="C43" s="13"/>
+      <c r="D43" s="13"/>
+      <c r="E43" s="13"/>
+      <c r="F43" s="13"/>
+      <c r="G43" s="13"/>
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="R1:R16" etc:filterBottomFollowUsedRange="0">
